--- a/grupos/2ALCM - Estadisticos 20222.xlsx
+++ b/grupos/2ALCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="186">
   <si>
     <t>Materia</t>
   </si>
@@ -1062,19 +1062,19 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>10</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G4">
         <v>9</v>
@@ -1116,19 +1116,19 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>10</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -1139,19 +1139,19 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>10</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G5">
         <v>9</v>
@@ -1193,19 +1193,19 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>10</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>9</v>
@@ -1216,19 +1216,19 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>7</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1270,19 +1270,19 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>7</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1293,19 +1293,19 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>5</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1347,19 +1347,19 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1370,19 +1370,19 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>6</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -1424,19 +1424,19 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1447,19 +1447,19 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D9">
         <v>10</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -1501,19 +1501,19 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>10</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1524,19 +1524,19 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>10</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>10</v>
@@ -1578,19 +1578,19 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>10</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1601,19 +1601,19 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>10</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G11">
         <v>9</v>
@@ -1655,19 +1655,19 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>10</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1678,19 +1678,19 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D12">
         <v>10</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G12">
         <v>9</v>
@@ -1732,19 +1732,19 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>10</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1755,19 +1755,19 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>9</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G13">
         <v>9</v>
@@ -1809,19 +1809,19 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1832,19 +1832,19 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D14">
         <v>10</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>8</v>
@@ -1886,19 +1886,19 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>10</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1909,19 +1909,19 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>10</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G15">
         <v>9</v>
@@ -1963,19 +1963,19 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>10</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1986,19 +1986,19 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>10</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G16">
         <v>8</v>
@@ -2040,19 +2040,19 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>10</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -2063,19 +2063,19 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D17">
         <v>9</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G17">
         <v>10</v>
@@ -2117,19 +2117,19 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -2140,19 +2140,19 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D18">
         <v>8</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -2194,19 +2194,19 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>8</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2217,19 +2217,19 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>7</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -2271,19 +2271,19 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>7</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2294,19 +2294,19 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>9</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G20">
         <v>8</v>
@@ -2348,19 +2348,19 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2371,19 +2371,19 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>5</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>6</v>
@@ -2425,19 +2425,19 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>5</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2448,19 +2448,19 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G22">
         <v>6</v>
@@ -2502,19 +2502,19 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>7</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2525,19 +2525,19 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>7</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -2579,19 +2579,19 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>7</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2602,19 +2602,19 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D24">
         <v>10</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G24">
         <v>6</v>
@@ -2656,19 +2656,19 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>10</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2679,19 +2679,19 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D25">
         <v>10</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G25">
         <v>10</v>
@@ -2733,19 +2733,19 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2756,19 +2756,19 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D26">
         <v>10</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G26">
         <v>8</v>
@@ -2810,19 +2810,19 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>10</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2833,19 +2833,19 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D27">
         <v>10</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>10</v>
@@ -2887,19 +2887,19 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>10</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2910,19 +2910,19 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D28">
         <v>5</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>7</v>
@@ -2964,19 +2964,19 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>5</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2987,19 +2987,19 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D29">
         <v>10</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G29">
         <v>9</v>
@@ -3041,19 +3041,19 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>10</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -3064,19 +3064,19 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D30">
         <v>7</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G30">
         <v>7</v>
@@ -3118,19 +3118,19 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>7</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3141,19 +3141,19 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>7</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G31">
         <v>9</v>
@@ -3195,19 +3195,19 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>7</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -3218,19 +3218,19 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D32">
         <v>10</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -3272,19 +3272,19 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>10</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3295,19 +3295,19 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D33">
         <v>10</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G33">
         <v>10</v>
@@ -3349,19 +3349,19 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>10</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -3372,19 +3372,19 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D34">
         <v>7</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G34">
         <v>10</v>
@@ -3426,19 +3426,19 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>7</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -3449,19 +3449,19 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D35">
         <v>10</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G35">
         <v>8</v>
@@ -3503,19 +3503,19 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>10</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>8</v>
@@ -3526,19 +3526,19 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D36">
         <v>10</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G36">
         <v>4</v>
@@ -3580,19 +3580,19 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V36">
         <v>10</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -3603,19 +3603,19 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D37">
         <v>10</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G37">
         <v>10</v>
@@ -3657,19 +3657,19 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>10</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>10</v>
@@ -3680,19 +3680,19 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D38">
         <v>5</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G38">
         <v>3</v>
@@ -3734,19 +3734,19 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V38">
         <v>5</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y38">
         <v>5</v>
@@ -3757,19 +3757,19 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D39">
         <v>10</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G39">
         <v>10</v>
@@ -3811,19 +3811,19 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
         <v>10</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y39">
         <v>10</v>
@@ -3834,19 +3834,19 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D40">
         <v>10</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G40">
         <v>10</v>
@@ -3888,19 +3888,19 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V40">
         <v>10</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y40">
         <v>10</v>
@@ -3911,19 +3911,19 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D41">
         <v>9</v>
       </c>
       <c r="E41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G41">
         <v>9</v>
@@ -3965,19 +3965,19 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V41">
         <v>9</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y41">
         <v>9</v>
@@ -3988,19 +3988,19 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D42">
         <v>10</v>
       </c>
       <c r="E42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G42">
         <v>10</v>
@@ -4042,19 +4042,19 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V42">
         <v>10</v>
       </c>
       <c r="W42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y42">
         <v>10</v>
@@ -4065,19 +4065,19 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D43">
         <v>5</v>
       </c>
       <c r="E43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G43">
         <v>9</v>
@@ -4119,19 +4119,19 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V43">
         <v>5</v>
       </c>
       <c r="W43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y43">
         <v>9</v>
@@ -4142,19 +4142,19 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D44">
         <v>7</v>
       </c>
       <c r="E44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G44">
         <v>8</v>
@@ -4196,19 +4196,19 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V44">
         <v>7</v>
       </c>
       <c r="W44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y44">
         <v>8</v>
@@ -4219,19 +4219,19 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D45">
         <v>10</v>
       </c>
       <c r="E45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G45">
         <v>9</v>
@@ -4273,19 +4273,19 @@
         <v>-1</v>
       </c>
       <c r="T45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V45">
         <v>10</v>
       </c>
       <c r="W45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y45">
         <v>9</v>
@@ -4296,19 +4296,19 @@
         <v>54</v>
       </c>
       <c r="B46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D46">
         <v>10</v>
       </c>
       <c r="E46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G46">
         <v>10</v>
@@ -4350,19 +4350,19 @@
         <v>-1</v>
       </c>
       <c r="T46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V46">
         <v>10</v>
       </c>
       <c r="W46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y46">
         <v>10</v>
@@ -4483,19 +4483,19 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>100</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -4542,19 +4542,19 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>100</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -4601,19 +4601,19 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>100</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>96.7</v>
@@ -4660,19 +4660,19 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D7">
         <v>15</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -4719,19 +4719,19 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>90</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -4778,19 +4778,19 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>100</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -4837,19 +4837,19 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>90</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>100</v>
@@ -4896,19 +4896,19 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>95</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -4955,19 +4955,19 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>95</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -5014,19 +5014,19 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>95</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -5073,19 +5073,19 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>100</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>100</v>
@@ -5132,19 +5132,19 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>85</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -5191,19 +5191,19 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>100</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -5250,19 +5250,19 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>95</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -5309,19 +5309,19 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>90</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G18">
         <v>100</v>
@@ -5368,19 +5368,19 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>95</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -5427,19 +5427,19 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>85</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>100</v>
@@ -5486,19 +5486,19 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>100</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>100</v>
@@ -5545,19 +5545,19 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>100</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>100</v>
@@ -5604,19 +5604,19 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>80</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>93.3</v>
@@ -5663,19 +5663,19 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>100</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -5722,19 +5722,19 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>100</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>100</v>
@@ -5781,19 +5781,19 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>100</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26">
         <v>100</v>
@@ -5840,19 +5840,19 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>100</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -5899,19 +5899,19 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>90</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G28">
         <v>100</v>
@@ -5958,19 +5958,19 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>95</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>100</v>
@@ -6017,19 +6017,19 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>95</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>100</v>
@@ -6076,19 +6076,19 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>100</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>100</v>
@@ -6135,19 +6135,19 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>100</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>100</v>
@@ -6194,19 +6194,19 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>100</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>100</v>
@@ -6253,19 +6253,19 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>100</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>100</v>
@@ -6312,19 +6312,19 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>100</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G35">
         <v>100</v>
@@ -6371,19 +6371,19 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>80</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G36">
         <v>100</v>
@@ -6430,19 +6430,19 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>100</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>100</v>
@@ -6489,19 +6489,19 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D38">
         <v>25</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G38">
         <v>83.3</v>
@@ -6548,19 +6548,19 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>100</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G39">
         <v>100</v>
@@ -6607,19 +6607,19 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D40">
         <v>100</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G40">
         <v>100</v>
@@ -6666,19 +6666,19 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D41">
         <v>95</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G41">
         <v>100</v>
@@ -6725,19 +6725,19 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D42">
         <v>100</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42">
         <v>100</v>
@@ -6784,19 +6784,19 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D43">
         <v>90</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G43">
         <v>100</v>
@@ -6843,19 +6843,19 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D44">
         <v>100</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G44">
         <v>100</v>
@@ -6902,19 +6902,19 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D45">
         <v>95</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G45">
         <v>100</v>
@@ -6961,19 +6961,19 @@
         <v>54</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D46">
         <v>100</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G46">
         <v>100</v>
@@ -7067,7 +7067,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
@@ -7076,27 +7076,30 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>86.05</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>13.95</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
       <c r="I2">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -7105,56 +7108,62 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>86.05</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>13.95</v>
+      </c>
+      <c r="H3">
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4">
         <v>43</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>88.37</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>11.63</v>
+      </c>
+      <c r="H4">
+        <v>8.6</v>
       </c>
       <c r="I4">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -7163,27 +7172,30 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>90.7</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H5">
+        <v>7.5</v>
       </c>
       <c r="I5">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
@@ -7192,19 +7204,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>86.05</v>
+        <v>93.02</v>
       </c>
       <c r="G6">
-        <v>13.95</v>
+        <v>6.98</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7215,25 +7227,25 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7">
         <v>43</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>88.37</v>
+        <v>97.67</v>
       </c>
       <c r="G7">
-        <v>11.63</v>
+        <v>2.33</v>
       </c>
       <c r="H7">
         <v>8.6</v>
@@ -7252,7 +7264,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F173"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7277,3446 +7289,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920086</v>
-      </c>
-      <c r="B2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920086</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920086</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920086</v>
-      </c>
-      <c r="B5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920085</v>
-      </c>
-      <c r="B6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920085</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920085</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" t="s">
-        <v>144</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920085</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920087</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D10" t="s">
-        <v>145</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920087</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" t="s">
-        <v>145</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920087</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" t="s">
-        <v>145</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920087</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920337</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" t="s">
-        <v>146</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920337</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" t="s">
-        <v>146</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920337</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" t="s">
-        <v>146</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920337</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>112</v>
-      </c>
-      <c r="D17" t="s">
-        <v>146</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920090</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" t="s">
-        <v>147</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920090</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" t="s">
-        <v>147</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920090</v>
-      </c>
-      <c r="B20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" t="s">
-        <v>147</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920090</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" t="s">
-        <v>147</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920091</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920091</v>
-      </c>
-      <c r="B23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" t="s">
-        <v>148</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920091</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" t="s">
-        <v>148</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920091</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" t="s">
-        <v>148</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920092</v>
-      </c>
-      <c r="B26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" t="s">
-        <v>149</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920092</v>
-      </c>
-      <c r="B27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>114</v>
-      </c>
-      <c r="D27" t="s">
-        <v>149</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920092</v>
-      </c>
-      <c r="B28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" t="s">
-        <v>114</v>
-      </c>
-      <c r="D28" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920092</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" t="s">
-        <v>114</v>
-      </c>
-      <c r="D29" t="s">
-        <v>149</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920338</v>
-      </c>
-      <c r="B30" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" t="s">
-        <v>150</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920338</v>
-      </c>
-      <c r="B31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" t="s">
-        <v>150</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920338</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" t="s">
-        <v>150</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920338</v>
-      </c>
-      <c r="B33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" t="s">
-        <v>150</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920093</v>
-      </c>
-      <c r="B34" t="s">
-        <v>79</v>
-      </c>
-      <c r="C34" t="s">
-        <v>115</v>
-      </c>
-      <c r="D34" t="s">
-        <v>151</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920093</v>
-      </c>
-      <c r="B35" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" t="s">
-        <v>115</v>
-      </c>
-      <c r="D35" t="s">
-        <v>151</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920093</v>
-      </c>
-      <c r="B36" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" t="s">
-        <v>115</v>
-      </c>
-      <c r="D36" t="s">
-        <v>151</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920093</v>
-      </c>
-      <c r="B37" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" t="s">
-        <v>115</v>
-      </c>
-      <c r="D37" t="s">
-        <v>151</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>22330051920094</v>
-      </c>
-      <c r="B38" t="s">
-        <v>79</v>
-      </c>
-      <c r="C38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D38" t="s">
-        <v>152</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>22330051920094</v>
-      </c>
-      <c r="B39" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" t="s">
-        <v>116</v>
-      </c>
-      <c r="D39" t="s">
-        <v>152</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>22330051920094</v>
-      </c>
-      <c r="B40" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" t="s">
-        <v>116</v>
-      </c>
-      <c r="D40" t="s">
-        <v>152</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>22330051920094</v>
-      </c>
-      <c r="B41" t="s">
-        <v>79</v>
-      </c>
-      <c r="C41" t="s">
-        <v>116</v>
-      </c>
-      <c r="D41" t="s">
-        <v>152</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>22330051920095</v>
-      </c>
-      <c r="B42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42" t="s">
-        <v>103</v>
-      </c>
-      <c r="D42" t="s">
-        <v>153</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>22330051920095</v>
-      </c>
-      <c r="B43" t="s">
-        <v>79</v>
-      </c>
-      <c r="C43" t="s">
-        <v>103</v>
-      </c>
-      <c r="D43" t="s">
-        <v>153</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>22330051920095</v>
-      </c>
-      <c r="B44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" t="s">
-        <v>153</v>
-      </c>
-      <c r="E44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>22330051920095</v>
-      </c>
-      <c r="B45" t="s">
-        <v>79</v>
-      </c>
-      <c r="C45" t="s">
-        <v>103</v>
-      </c>
-      <c r="D45" t="s">
-        <v>153</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>22330051920096</v>
-      </c>
-      <c r="B46" t="s">
-        <v>81</v>
-      </c>
-      <c r="C46" t="s">
-        <v>117</v>
-      </c>
-      <c r="D46" t="s">
-        <v>154</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>22330051920096</v>
-      </c>
-      <c r="B47" t="s">
-        <v>81</v>
-      </c>
-      <c r="C47" t="s">
-        <v>117</v>
-      </c>
-      <c r="D47" t="s">
-        <v>154</v>
-      </c>
-      <c r="E47" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>22330051920096</v>
-      </c>
-      <c r="B48" t="s">
-        <v>81</v>
-      </c>
-      <c r="C48" t="s">
-        <v>117</v>
-      </c>
-      <c r="D48" t="s">
-        <v>154</v>
-      </c>
-      <c r="E48" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>22330051920096</v>
-      </c>
-      <c r="B49" t="s">
-        <v>81</v>
-      </c>
-      <c r="C49" t="s">
-        <v>117</v>
-      </c>
-      <c r="D49" t="s">
-        <v>154</v>
-      </c>
-      <c r="E49" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>22330051920097</v>
-      </c>
-      <c r="B50" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" t="s">
-        <v>118</v>
-      </c>
-      <c r="D50" t="s">
-        <v>155</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>22330051920097</v>
-      </c>
-      <c r="B51" t="s">
-        <v>81</v>
-      </c>
-      <c r="C51" t="s">
-        <v>118</v>
-      </c>
-      <c r="D51" t="s">
-        <v>155</v>
-      </c>
-      <c r="E51" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>22330051920097</v>
-      </c>
-      <c r="B52" t="s">
-        <v>81</v>
-      </c>
-      <c r="C52" t="s">
-        <v>118</v>
-      </c>
-      <c r="D52" t="s">
-        <v>155</v>
-      </c>
-      <c r="E52" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>22330051920097</v>
-      </c>
-      <c r="B53" t="s">
-        <v>81</v>
-      </c>
-      <c r="C53" t="s">
-        <v>118</v>
-      </c>
-      <c r="D53" t="s">
-        <v>155</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>22330051920098</v>
-      </c>
-      <c r="B54" t="s">
-        <v>81</v>
-      </c>
-      <c r="C54" t="s">
-        <v>119</v>
-      </c>
-      <c r="D54" t="s">
-        <v>156</v>
-      </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>22330051920098</v>
-      </c>
-      <c r="B55" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" t="s">
-        <v>119</v>
-      </c>
-      <c r="D55" t="s">
-        <v>156</v>
-      </c>
-      <c r="E55" t="s">
-        <v>6</v>
-      </c>
-      <c r="F55" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>22330051920098</v>
-      </c>
-      <c r="B56" t="s">
-        <v>81</v>
-      </c>
-      <c r="C56" t="s">
-        <v>119</v>
-      </c>
-      <c r="D56" t="s">
-        <v>156</v>
-      </c>
-      <c r="E56" t="s">
-        <v>5</v>
-      </c>
-      <c r="F56" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>22330051920098</v>
-      </c>
-      <c r="B57" t="s">
-        <v>81</v>
-      </c>
-      <c r="C57" t="s">
-        <v>119</v>
-      </c>
-      <c r="D57" t="s">
-        <v>156</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>22330051920339</v>
-      </c>
-      <c r="B58" t="s">
-        <v>82</v>
-      </c>
-      <c r="C58" t="s">
-        <v>103</v>
-      </c>
-      <c r="D58" t="s">
-        <v>157</v>
-      </c>
-      <c r="E58" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>22330051920339</v>
-      </c>
-      <c r="B59" t="s">
-        <v>82</v>
-      </c>
-      <c r="C59" t="s">
-        <v>103</v>
-      </c>
-      <c r="D59" t="s">
-        <v>157</v>
-      </c>
-      <c r="E59" t="s">
-        <v>6</v>
-      </c>
-      <c r="F59" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>22330051920339</v>
-      </c>
-      <c r="B60" t="s">
-        <v>82</v>
-      </c>
-      <c r="C60" t="s">
-        <v>103</v>
-      </c>
-      <c r="D60" t="s">
-        <v>157</v>
-      </c>
-      <c r="E60" t="s">
-        <v>5</v>
-      </c>
-      <c r="F60" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>22330051920339</v>
-      </c>
-      <c r="B61" t="s">
-        <v>82</v>
-      </c>
-      <c r="C61" t="s">
-        <v>103</v>
-      </c>
-      <c r="D61" t="s">
-        <v>157</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>22330051920088</v>
-      </c>
-      <c r="B62" t="s">
-        <v>83</v>
-      </c>
-      <c r="C62" t="s">
-        <v>120</v>
-      </c>
-      <c r="D62" t="s">
-        <v>158</v>
-      </c>
-      <c r="E62" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>22330051920088</v>
-      </c>
-      <c r="B63" t="s">
-        <v>83</v>
-      </c>
-      <c r="C63" t="s">
-        <v>120</v>
-      </c>
-      <c r="D63" t="s">
-        <v>158</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>22330051920088</v>
-      </c>
-      <c r="B64" t="s">
-        <v>83</v>
-      </c>
-      <c r="C64" t="s">
-        <v>120</v>
-      </c>
-      <c r="D64" t="s">
-        <v>158</v>
-      </c>
-      <c r="E64" t="s">
-        <v>5</v>
-      </c>
-      <c r="F64" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>22330051920088</v>
-      </c>
-      <c r="B65" t="s">
-        <v>83</v>
-      </c>
-      <c r="C65" t="s">
-        <v>120</v>
-      </c>
-      <c r="D65" t="s">
-        <v>158</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>22330051920340</v>
-      </c>
-      <c r="B66" t="s">
-        <v>84</v>
-      </c>
-      <c r="C66" t="s">
-        <v>80</v>
-      </c>
-      <c r="D66" t="s">
-        <v>159</v>
-      </c>
-      <c r="E66" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>22330051920340</v>
-      </c>
-      <c r="B67" t="s">
-        <v>84</v>
-      </c>
-      <c r="C67" t="s">
-        <v>80</v>
-      </c>
-      <c r="D67" t="s">
-        <v>159</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>22330051920340</v>
-      </c>
-      <c r="B68" t="s">
-        <v>84</v>
-      </c>
-      <c r="C68" t="s">
-        <v>80</v>
-      </c>
-      <c r="D68" t="s">
-        <v>159</v>
-      </c>
-      <c r="E68" t="s">
-        <v>5</v>
-      </c>
-      <c r="F68" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>22330051920340</v>
-      </c>
-      <c r="B69" t="s">
-        <v>84</v>
-      </c>
-      <c r="C69" t="s">
-        <v>80</v>
-      </c>
-      <c r="D69" t="s">
-        <v>159</v>
-      </c>
-      <c r="E69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>22330051920099</v>
-      </c>
-      <c r="B70" t="s">
-        <v>85</v>
-      </c>
-      <c r="C70" t="s">
-        <v>121</v>
-      </c>
-      <c r="D70" t="s">
-        <v>160</v>
-      </c>
-      <c r="E70" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>22330051920099</v>
-      </c>
-      <c r="B71" t="s">
-        <v>85</v>
-      </c>
-      <c r="C71" t="s">
-        <v>121</v>
-      </c>
-      <c r="D71" t="s">
-        <v>160</v>
-      </c>
-      <c r="E71" t="s">
-        <v>6</v>
-      </c>
-      <c r="F71" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>22330051920099</v>
-      </c>
-      <c r="B72" t="s">
-        <v>85</v>
-      </c>
-      <c r="C72" t="s">
-        <v>121</v>
-      </c>
-      <c r="D72" t="s">
-        <v>160</v>
-      </c>
-      <c r="E72" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>22330051920099</v>
-      </c>
-      <c r="B73" t="s">
-        <v>85</v>
-      </c>
-      <c r="C73" t="s">
-        <v>121</v>
-      </c>
-      <c r="D73" t="s">
-        <v>160</v>
-      </c>
-      <c r="E73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>22330051920100</v>
-      </c>
-      <c r="B74" t="s">
-        <v>86</v>
-      </c>
-      <c r="C74" t="s">
-        <v>122</v>
-      </c>
-      <c r="D74" t="s">
-        <v>161</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>22330051920100</v>
-      </c>
-      <c r="B75" t="s">
-        <v>86</v>
-      </c>
-      <c r="C75" t="s">
-        <v>122</v>
-      </c>
-      <c r="D75" t="s">
-        <v>161</v>
-      </c>
-      <c r="E75" t="s">
-        <v>6</v>
-      </c>
-      <c r="F75" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>22330051920100</v>
-      </c>
-      <c r="B76" t="s">
-        <v>86</v>
-      </c>
-      <c r="C76" t="s">
-        <v>122</v>
-      </c>
-      <c r="D76" t="s">
-        <v>161</v>
-      </c>
-      <c r="E76" t="s">
-        <v>5</v>
-      </c>
-      <c r="F76" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>22330051920100</v>
-      </c>
-      <c r="B77" t="s">
-        <v>86</v>
-      </c>
-      <c r="C77" t="s">
-        <v>122</v>
-      </c>
-      <c r="D77" t="s">
-        <v>161</v>
-      </c>
-      <c r="E77" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>22330051920101</v>
-      </c>
-      <c r="B78" t="s">
-        <v>86</v>
-      </c>
-      <c r="C78" t="s">
-        <v>98</v>
-      </c>
-      <c r="D78" t="s">
-        <v>162</v>
-      </c>
-      <c r="E78" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>22330051920101</v>
-      </c>
-      <c r="B79" t="s">
-        <v>86</v>
-      </c>
-      <c r="C79" t="s">
-        <v>98</v>
-      </c>
-      <c r="D79" t="s">
-        <v>162</v>
-      </c>
-      <c r="E79" t="s">
-        <v>6</v>
-      </c>
-      <c r="F79" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>22330051920101</v>
-      </c>
-      <c r="B80" t="s">
-        <v>86</v>
-      </c>
-      <c r="C80" t="s">
-        <v>98</v>
-      </c>
-      <c r="D80" t="s">
-        <v>162</v>
-      </c>
-      <c r="E80" t="s">
-        <v>5</v>
-      </c>
-      <c r="F80" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>22330051920101</v>
-      </c>
-      <c r="B81" t="s">
-        <v>86</v>
-      </c>
-      <c r="C81" t="s">
-        <v>98</v>
-      </c>
-      <c r="D81" t="s">
-        <v>162</v>
-      </c>
-      <c r="E81" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>22330051920089</v>
-      </c>
-      <c r="B82" t="s">
-        <v>87</v>
-      </c>
-      <c r="C82" t="s">
-        <v>123</v>
-      </c>
-      <c r="D82" t="s">
-        <v>163</v>
-      </c>
-      <c r="E82" t="s">
-        <v>9</v>
-      </c>
-      <c r="F82" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>22330051920089</v>
-      </c>
-      <c r="B83" t="s">
-        <v>87</v>
-      </c>
-      <c r="C83" t="s">
-        <v>123</v>
-      </c>
-      <c r="D83" t="s">
-        <v>163</v>
-      </c>
-      <c r="E83" t="s">
-        <v>6</v>
-      </c>
-      <c r="F83" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>22330051920089</v>
-      </c>
-      <c r="B84" t="s">
-        <v>87</v>
-      </c>
-      <c r="C84" t="s">
-        <v>123</v>
-      </c>
-      <c r="D84" t="s">
-        <v>163</v>
-      </c>
-      <c r="E84" t="s">
-        <v>5</v>
-      </c>
-      <c r="F84" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>22330051920089</v>
-      </c>
-      <c r="B85" t="s">
-        <v>87</v>
-      </c>
-      <c r="C85" t="s">
-        <v>123</v>
-      </c>
-      <c r="D85" t="s">
-        <v>163</v>
-      </c>
-      <c r="E85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>22330051920102</v>
-      </c>
-      <c r="B86" t="s">
-        <v>88</v>
-      </c>
-      <c r="C86" t="s">
-        <v>124</v>
-      </c>
-      <c r="D86" t="s">
-        <v>164</v>
-      </c>
-      <c r="E86" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>22330051920102</v>
-      </c>
-      <c r="B87" t="s">
-        <v>88</v>
-      </c>
-      <c r="C87" t="s">
-        <v>124</v>
-      </c>
-      <c r="D87" t="s">
-        <v>164</v>
-      </c>
-      <c r="E87" t="s">
-        <v>6</v>
-      </c>
-      <c r="F87" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>22330051920102</v>
-      </c>
-      <c r="B88" t="s">
-        <v>88</v>
-      </c>
-      <c r="C88" t="s">
-        <v>124</v>
-      </c>
-      <c r="D88" t="s">
-        <v>164</v>
-      </c>
-      <c r="E88" t="s">
-        <v>5</v>
-      </c>
-      <c r="F88" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>22330051920102</v>
-      </c>
-      <c r="B89" t="s">
-        <v>88</v>
-      </c>
-      <c r="C89" t="s">
-        <v>124</v>
-      </c>
-      <c r="D89" t="s">
-        <v>164</v>
-      </c>
-      <c r="E89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>22330051920103</v>
-      </c>
-      <c r="B90" t="s">
-        <v>89</v>
-      </c>
-      <c r="C90" t="s">
-        <v>125</v>
-      </c>
-      <c r="D90" t="s">
-        <v>165</v>
-      </c>
-      <c r="E90" t="s">
-        <v>9</v>
-      </c>
-      <c r="F90" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>22330051920103</v>
-      </c>
-      <c r="B91" t="s">
-        <v>89</v>
-      </c>
-      <c r="C91" t="s">
-        <v>125</v>
-      </c>
-      <c r="D91" t="s">
-        <v>165</v>
-      </c>
-      <c r="E91" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>22330051920103</v>
-      </c>
-      <c r="B92" t="s">
-        <v>89</v>
-      </c>
-      <c r="C92" t="s">
-        <v>125</v>
-      </c>
-      <c r="D92" t="s">
-        <v>165</v>
-      </c>
-      <c r="E92" t="s">
-        <v>5</v>
-      </c>
-      <c r="F92" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>22330051920103</v>
-      </c>
-      <c r="B93" t="s">
-        <v>89</v>
-      </c>
-      <c r="C93" t="s">
-        <v>125</v>
-      </c>
-      <c r="D93" t="s">
-        <v>165</v>
-      </c>
-      <c r="E93" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>22330051920105</v>
-      </c>
-      <c r="B94" t="s">
-        <v>90</v>
-      </c>
-      <c r="C94" t="s">
-        <v>126</v>
-      </c>
-      <c r="D94" t="s">
-        <v>166</v>
-      </c>
-      <c r="E94" t="s">
-        <v>9</v>
-      </c>
-      <c r="F94" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>22330051920105</v>
-      </c>
-      <c r="B95" t="s">
-        <v>90</v>
-      </c>
-      <c r="C95" t="s">
-        <v>126</v>
-      </c>
-      <c r="D95" t="s">
-        <v>166</v>
-      </c>
-      <c r="E95" t="s">
-        <v>6</v>
-      </c>
-      <c r="F95" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>22330051920105</v>
-      </c>
-      <c r="B96" t="s">
-        <v>90</v>
-      </c>
-      <c r="C96" t="s">
-        <v>126</v>
-      </c>
-      <c r="D96" t="s">
-        <v>166</v>
-      </c>
-      <c r="E96" t="s">
-        <v>5</v>
-      </c>
-      <c r="F96" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>22330051920105</v>
-      </c>
-      <c r="B97" t="s">
-        <v>90</v>
-      </c>
-      <c r="C97" t="s">
-        <v>126</v>
-      </c>
-      <c r="D97" t="s">
-        <v>166</v>
-      </c>
-      <c r="E97" t="s">
-        <v>8</v>
-      </c>
-      <c r="F97" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>22330051920104</v>
-      </c>
-      <c r="B98" t="s">
-        <v>91</v>
-      </c>
-      <c r="C98" t="s">
-        <v>127</v>
-      </c>
-      <c r="D98" t="s">
-        <v>167</v>
-      </c>
-      <c r="E98" t="s">
-        <v>9</v>
-      </c>
-      <c r="F98" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>22330051920104</v>
-      </c>
-      <c r="B99" t="s">
-        <v>91</v>
-      </c>
-      <c r="C99" t="s">
-        <v>127</v>
-      </c>
-      <c r="D99" t="s">
-        <v>167</v>
-      </c>
-      <c r="E99" t="s">
-        <v>6</v>
-      </c>
-      <c r="F99" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>22330051920104</v>
-      </c>
-      <c r="B100" t="s">
-        <v>91</v>
-      </c>
-      <c r="C100" t="s">
-        <v>127</v>
-      </c>
-      <c r="D100" t="s">
-        <v>167</v>
-      </c>
-      <c r="E100" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>22330051920104</v>
-      </c>
-      <c r="B101" t="s">
-        <v>91</v>
-      </c>
-      <c r="C101" t="s">
-        <v>127</v>
-      </c>
-      <c r="D101" t="s">
-        <v>167</v>
-      </c>
-      <c r="E101" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>22330051920106</v>
-      </c>
-      <c r="B102" t="s">
-        <v>92</v>
-      </c>
-      <c r="C102" t="s">
-        <v>128</v>
-      </c>
-      <c r="D102" t="s">
-        <v>168</v>
-      </c>
-      <c r="E102" t="s">
-        <v>9</v>
-      </c>
-      <c r="F102" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>22330051920106</v>
-      </c>
-      <c r="B103" t="s">
-        <v>92</v>
-      </c>
-      <c r="C103" t="s">
-        <v>128</v>
-      </c>
-      <c r="D103" t="s">
-        <v>168</v>
-      </c>
-      <c r="E103" t="s">
-        <v>6</v>
-      </c>
-      <c r="F103" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>22330051920106</v>
-      </c>
-      <c r="B104" t="s">
-        <v>92</v>
-      </c>
-      <c r="C104" t="s">
-        <v>128</v>
-      </c>
-      <c r="D104" t="s">
-        <v>168</v>
-      </c>
-      <c r="E104" t="s">
-        <v>5</v>
-      </c>
-      <c r="F104" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>22330051920106</v>
-      </c>
-      <c r="B105" t="s">
-        <v>92</v>
-      </c>
-      <c r="C105" t="s">
-        <v>128</v>
-      </c>
-      <c r="D105" t="s">
-        <v>168</v>
-      </c>
-      <c r="E105" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>22330051920108</v>
-      </c>
-      <c r="B106" t="s">
-        <v>93</v>
-      </c>
-      <c r="C106" t="s">
-        <v>99</v>
-      </c>
-      <c r="D106" t="s">
-        <v>169</v>
-      </c>
-      <c r="E106" t="s">
-        <v>9</v>
-      </c>
-      <c r="F106" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>22330051920108</v>
-      </c>
-      <c r="B107" t="s">
-        <v>93</v>
-      </c>
-      <c r="C107" t="s">
-        <v>99</v>
-      </c>
-      <c r="D107" t="s">
-        <v>169</v>
-      </c>
-      <c r="E107" t="s">
-        <v>6</v>
-      </c>
-      <c r="F107" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>22330051920108</v>
-      </c>
-      <c r="B108" t="s">
-        <v>93</v>
-      </c>
-      <c r="C108" t="s">
-        <v>99</v>
-      </c>
-      <c r="D108" t="s">
-        <v>169</v>
-      </c>
-      <c r="E108" t="s">
-        <v>5</v>
-      </c>
-      <c r="F108" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>22330051920108</v>
-      </c>
-      <c r="B109" t="s">
-        <v>93</v>
-      </c>
-      <c r="C109" t="s">
-        <v>99</v>
-      </c>
-      <c r="D109" t="s">
-        <v>169</v>
-      </c>
-      <c r="E109" t="s">
-        <v>8</v>
-      </c>
-      <c r="F109" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>22330051920107</v>
-      </c>
-      <c r="B110" t="s">
-        <v>94</v>
-      </c>
-      <c r="C110" t="s">
-        <v>126</v>
-      </c>
-      <c r="D110" t="s">
-        <v>170</v>
-      </c>
-      <c r="E110" t="s">
-        <v>9</v>
-      </c>
-      <c r="F110" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>22330051920107</v>
-      </c>
-      <c r="B111" t="s">
-        <v>94</v>
-      </c>
-      <c r="C111" t="s">
-        <v>126</v>
-      </c>
-      <c r="D111" t="s">
-        <v>170</v>
-      </c>
-      <c r="E111" t="s">
-        <v>6</v>
-      </c>
-      <c r="F111" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>22330051920107</v>
-      </c>
-      <c r="B112" t="s">
-        <v>94</v>
-      </c>
-      <c r="C112" t="s">
-        <v>126</v>
-      </c>
-      <c r="D112" t="s">
-        <v>170</v>
-      </c>
-      <c r="E112" t="s">
-        <v>5</v>
-      </c>
-      <c r="F112" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>22330051920107</v>
-      </c>
-      <c r="B113" t="s">
-        <v>94</v>
-      </c>
-      <c r="C113" t="s">
-        <v>126</v>
-      </c>
-      <c r="D113" t="s">
-        <v>170</v>
-      </c>
-      <c r="E113" t="s">
-        <v>8</v>
-      </c>
-      <c r="F113" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>22330051920109</v>
-      </c>
-      <c r="B114" t="s">
-        <v>95</v>
-      </c>
-      <c r="C114" t="s">
-        <v>129</v>
-      </c>
-      <c r="D114" t="s">
-        <v>171</v>
-      </c>
-      <c r="E114" t="s">
-        <v>9</v>
-      </c>
-      <c r="F114" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>22330051920109</v>
-      </c>
-      <c r="B115" t="s">
-        <v>95</v>
-      </c>
-      <c r="C115" t="s">
-        <v>129</v>
-      </c>
-      <c r="D115" t="s">
-        <v>171</v>
-      </c>
-      <c r="E115" t="s">
-        <v>6</v>
-      </c>
-      <c r="F115" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>22330051920109</v>
-      </c>
-      <c r="B116" t="s">
-        <v>95</v>
-      </c>
-      <c r="C116" t="s">
-        <v>129</v>
-      </c>
-      <c r="D116" t="s">
-        <v>171</v>
-      </c>
-      <c r="E116" t="s">
-        <v>5</v>
-      </c>
-      <c r="F116" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>22330051920109</v>
-      </c>
-      <c r="B117" t="s">
-        <v>95</v>
-      </c>
-      <c r="C117" t="s">
-        <v>129</v>
-      </c>
-      <c r="D117" t="s">
-        <v>171</v>
-      </c>
-      <c r="E117" t="s">
-        <v>8</v>
-      </c>
-      <c r="F117" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>22330051920111</v>
-      </c>
-      <c r="B118" t="s">
-        <v>96</v>
-      </c>
-      <c r="C118" t="s">
-        <v>130</v>
-      </c>
-      <c r="D118" t="s">
-        <v>172</v>
-      </c>
-      <c r="E118" t="s">
-        <v>9</v>
-      </c>
-      <c r="F118" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>22330051920111</v>
-      </c>
-      <c r="B119" t="s">
-        <v>96</v>
-      </c>
-      <c r="C119" t="s">
-        <v>130</v>
-      </c>
-      <c r="D119" t="s">
-        <v>172</v>
-      </c>
-      <c r="E119" t="s">
-        <v>6</v>
-      </c>
-      <c r="F119" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>22330051920111</v>
-      </c>
-      <c r="B120" t="s">
-        <v>96</v>
-      </c>
-      <c r="C120" t="s">
-        <v>130</v>
-      </c>
-      <c r="D120" t="s">
-        <v>172</v>
-      </c>
-      <c r="E120" t="s">
-        <v>5</v>
-      </c>
-      <c r="F120" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>22330051920111</v>
-      </c>
-      <c r="B121" t="s">
-        <v>96</v>
-      </c>
-      <c r="C121" t="s">
-        <v>130</v>
-      </c>
-      <c r="D121" t="s">
-        <v>172</v>
-      </c>
-      <c r="E121" t="s">
-        <v>8</v>
-      </c>
-      <c r="F121" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>22330051920112</v>
-      </c>
-      <c r="B122" t="s">
-        <v>97</v>
-      </c>
-      <c r="C122" t="s">
-        <v>103</v>
-      </c>
-      <c r="D122" t="s">
-        <v>173</v>
-      </c>
-      <c r="E122" t="s">
-        <v>9</v>
-      </c>
-      <c r="F122" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>22330051920112</v>
-      </c>
-      <c r="B123" t="s">
-        <v>97</v>
-      </c>
-      <c r="C123" t="s">
-        <v>103</v>
-      </c>
-      <c r="D123" t="s">
-        <v>173</v>
-      </c>
-      <c r="E123" t="s">
-        <v>6</v>
-      </c>
-      <c r="F123" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>22330051920112</v>
-      </c>
-      <c r="B124" t="s">
-        <v>97</v>
-      </c>
-      <c r="C124" t="s">
-        <v>103</v>
-      </c>
-      <c r="D124" t="s">
-        <v>173</v>
-      </c>
-      <c r="E124" t="s">
-        <v>5</v>
-      </c>
-      <c r="F124" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>22330051920112</v>
-      </c>
-      <c r="B125" t="s">
-        <v>97</v>
-      </c>
-      <c r="C125" t="s">
-        <v>103</v>
-      </c>
-      <c r="D125" t="s">
-        <v>173</v>
-      </c>
-      <c r="E125" t="s">
-        <v>8</v>
-      </c>
-      <c r="F125" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>22330051920113</v>
-      </c>
-      <c r="B126" t="s">
-        <v>97</v>
-      </c>
-      <c r="C126" t="s">
-        <v>131</v>
-      </c>
-      <c r="D126" t="s">
-        <v>174</v>
-      </c>
-      <c r="E126" t="s">
-        <v>9</v>
-      </c>
-      <c r="F126" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>22330051920113</v>
-      </c>
-      <c r="B127" t="s">
-        <v>97</v>
-      </c>
-      <c r="C127" t="s">
-        <v>131</v>
-      </c>
-      <c r="D127" t="s">
-        <v>174</v>
-      </c>
-      <c r="E127" t="s">
-        <v>6</v>
-      </c>
-      <c r="F127" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>22330051920113</v>
-      </c>
-      <c r="B128" t="s">
-        <v>97</v>
-      </c>
-      <c r="C128" t="s">
-        <v>131</v>
-      </c>
-      <c r="D128" t="s">
-        <v>174</v>
-      </c>
-      <c r="E128" t="s">
-        <v>5</v>
-      </c>
-      <c r="F128" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>22330051920113</v>
-      </c>
-      <c r="B129" t="s">
-        <v>97</v>
-      </c>
-      <c r="C129" t="s">
-        <v>131</v>
-      </c>
-      <c r="D129" t="s">
-        <v>174</v>
-      </c>
-      <c r="E129" t="s">
-        <v>8</v>
-      </c>
-      <c r="F129" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>22330051920114</v>
-      </c>
-      <c r="B130" t="s">
-        <v>98</v>
-      </c>
-      <c r="C130" t="s">
-        <v>132</v>
-      </c>
-      <c r="D130" t="s">
-        <v>175</v>
-      </c>
-      <c r="E130" t="s">
-        <v>9</v>
-      </c>
-      <c r="F130" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
-        <v>22330051920114</v>
-      </c>
-      <c r="B131" t="s">
-        <v>98</v>
-      </c>
-      <c r="C131" t="s">
-        <v>132</v>
-      </c>
-      <c r="D131" t="s">
-        <v>175</v>
-      </c>
-      <c r="E131" t="s">
-        <v>6</v>
-      </c>
-      <c r="F131" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132">
-        <v>22330051920114</v>
-      </c>
-      <c r="B132" t="s">
-        <v>98</v>
-      </c>
-      <c r="C132" t="s">
-        <v>132</v>
-      </c>
-      <c r="D132" t="s">
-        <v>175</v>
-      </c>
-      <c r="E132" t="s">
-        <v>5</v>
-      </c>
-      <c r="F132" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>22330051920114</v>
-      </c>
-      <c r="B133" t="s">
-        <v>98</v>
-      </c>
-      <c r="C133" t="s">
-        <v>132</v>
-      </c>
-      <c r="D133" t="s">
-        <v>175</v>
-      </c>
-      <c r="E133" t="s">
-        <v>8</v>
-      </c>
-      <c r="F133" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134">
-        <v>22330051920115</v>
-      </c>
-      <c r="B134" t="s">
-        <v>99</v>
-      </c>
-      <c r="C134" t="s">
-        <v>133</v>
-      </c>
-      <c r="D134" t="s">
-        <v>176</v>
-      </c>
-      <c r="E134" t="s">
-        <v>9</v>
-      </c>
-      <c r="F134" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135">
-        <v>22330051920115</v>
-      </c>
-      <c r="B135" t="s">
-        <v>99</v>
-      </c>
-      <c r="C135" t="s">
-        <v>133</v>
-      </c>
-      <c r="D135" t="s">
-        <v>176</v>
-      </c>
-      <c r="E135" t="s">
-        <v>6</v>
-      </c>
-      <c r="F135" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136">
-        <v>22330051920115</v>
-      </c>
-      <c r="B136" t="s">
-        <v>99</v>
-      </c>
-      <c r="C136" t="s">
-        <v>133</v>
-      </c>
-      <c r="D136" t="s">
-        <v>176</v>
-      </c>
-      <c r="E136" t="s">
-        <v>5</v>
-      </c>
-      <c r="F136" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137">
-        <v>22330051920115</v>
-      </c>
-      <c r="B137" t="s">
-        <v>99</v>
-      </c>
-      <c r="C137" t="s">
-        <v>133</v>
-      </c>
-      <c r="D137" t="s">
-        <v>176</v>
-      </c>
-      <c r="E137" t="s">
-        <v>8</v>
-      </c>
-      <c r="F137" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138">
-        <v>22330051920117</v>
-      </c>
-      <c r="B138" t="s">
-        <v>100</v>
-      </c>
-      <c r="C138" t="s">
-        <v>134</v>
-      </c>
-      <c r="D138" t="s">
-        <v>177</v>
-      </c>
-      <c r="E138" t="s">
-        <v>9</v>
-      </c>
-      <c r="F138" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139">
-        <v>22330051920117</v>
-      </c>
-      <c r="B139" t="s">
-        <v>100</v>
-      </c>
-      <c r="C139" t="s">
-        <v>134</v>
-      </c>
-      <c r="D139" t="s">
-        <v>177</v>
-      </c>
-      <c r="E139" t="s">
-        <v>6</v>
-      </c>
-      <c r="F139" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140">
-        <v>22330051920117</v>
-      </c>
-      <c r="B140" t="s">
-        <v>100</v>
-      </c>
-      <c r="C140" t="s">
-        <v>134</v>
-      </c>
-      <c r="D140" t="s">
-        <v>177</v>
-      </c>
-      <c r="E140" t="s">
-        <v>5</v>
-      </c>
-      <c r="F140" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141">
-        <v>22330051920117</v>
-      </c>
-      <c r="B141" t="s">
-        <v>100</v>
-      </c>
-      <c r="C141" t="s">
-        <v>134</v>
-      </c>
-      <c r="D141" t="s">
-        <v>177</v>
-      </c>
-      <c r="E141" t="s">
-        <v>8</v>
-      </c>
-      <c r="F141" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142">
-        <v>22330051920118</v>
-      </c>
-      <c r="B142" t="s">
-        <v>101</v>
-      </c>
-      <c r="C142" t="s">
-        <v>135</v>
-      </c>
-      <c r="D142" t="s">
-        <v>178</v>
-      </c>
-      <c r="E142" t="s">
-        <v>9</v>
-      </c>
-      <c r="F142" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143">
-        <v>22330051920118</v>
-      </c>
-      <c r="B143" t="s">
-        <v>101</v>
-      </c>
-      <c r="C143" t="s">
-        <v>135</v>
-      </c>
-      <c r="D143" t="s">
-        <v>178</v>
-      </c>
-      <c r="E143" t="s">
-        <v>6</v>
-      </c>
-      <c r="F143" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144">
-        <v>22330051920118</v>
-      </c>
-      <c r="B144" t="s">
-        <v>101</v>
-      </c>
-      <c r="C144" t="s">
-        <v>135</v>
-      </c>
-      <c r="D144" t="s">
-        <v>178</v>
-      </c>
-      <c r="E144" t="s">
-        <v>5</v>
-      </c>
-      <c r="F144" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145">
-        <v>22330051920118</v>
-      </c>
-      <c r="B145" t="s">
-        <v>101</v>
-      </c>
-      <c r="C145" t="s">
-        <v>135</v>
-      </c>
-      <c r="D145" t="s">
-        <v>178</v>
-      </c>
-      <c r="E145" t="s">
-        <v>8</v>
-      </c>
-      <c r="F145" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146">
-        <v>22330051920116</v>
-      </c>
-      <c r="B146" t="s">
-        <v>102</v>
-      </c>
-      <c r="C146" t="s">
-        <v>136</v>
-      </c>
-      <c r="D146" t="s">
-        <v>179</v>
-      </c>
-      <c r="E146" t="s">
-        <v>9</v>
-      </c>
-      <c r="F146" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147">
-        <v>22330051920116</v>
-      </c>
-      <c r="B147" t="s">
-        <v>102</v>
-      </c>
-      <c r="C147" t="s">
-        <v>136</v>
-      </c>
-      <c r="D147" t="s">
-        <v>179</v>
-      </c>
-      <c r="E147" t="s">
-        <v>6</v>
-      </c>
-      <c r="F147" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148">
-        <v>22330051920116</v>
-      </c>
-      <c r="B148" t="s">
-        <v>102</v>
-      </c>
-      <c r="C148" t="s">
-        <v>136</v>
-      </c>
-      <c r="D148" t="s">
-        <v>179</v>
-      </c>
-      <c r="E148" t="s">
-        <v>5</v>
-      </c>
-      <c r="F148" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149">
-        <v>22330051920116</v>
-      </c>
-      <c r="B149" t="s">
-        <v>102</v>
-      </c>
-      <c r="C149" t="s">
-        <v>136</v>
-      </c>
-      <c r="D149" t="s">
-        <v>179</v>
-      </c>
-      <c r="E149" t="s">
-        <v>8</v>
-      </c>
-      <c r="F149" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150">
-        <v>22330051920119</v>
-      </c>
-      <c r="B150" t="s">
-        <v>103</v>
-      </c>
-      <c r="C150" t="s">
-        <v>137</v>
-      </c>
-      <c r="D150" t="s">
-        <v>180</v>
-      </c>
-      <c r="E150" t="s">
-        <v>9</v>
-      </c>
-      <c r="F150" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151">
-        <v>22330051920119</v>
-      </c>
-      <c r="B151" t="s">
-        <v>103</v>
-      </c>
-      <c r="C151" t="s">
-        <v>137</v>
-      </c>
-      <c r="D151" t="s">
-        <v>180</v>
-      </c>
-      <c r="E151" t="s">
-        <v>6</v>
-      </c>
-      <c r="F151" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152">
-        <v>22330051920119</v>
-      </c>
-      <c r="B152" t="s">
-        <v>103</v>
-      </c>
-      <c r="C152" t="s">
-        <v>137</v>
-      </c>
-      <c r="D152" t="s">
-        <v>180</v>
-      </c>
-      <c r="E152" t="s">
-        <v>5</v>
-      </c>
-      <c r="F152" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153">
-        <v>22330051920119</v>
-      </c>
-      <c r="B153" t="s">
-        <v>103</v>
-      </c>
-      <c r="C153" t="s">
-        <v>137</v>
-      </c>
-      <c r="D153" t="s">
-        <v>180</v>
-      </c>
-      <c r="E153" t="s">
-        <v>8</v>
-      </c>
-      <c r="F153" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154">
-        <v>22330051920120</v>
-      </c>
-      <c r="B154" t="s">
-        <v>104</v>
-      </c>
-      <c r="C154" t="s">
-        <v>138</v>
-      </c>
-      <c r="D154" t="s">
-        <v>181</v>
-      </c>
-      <c r="E154" t="s">
-        <v>9</v>
-      </c>
-      <c r="F154" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155">
-        <v>22330051920120</v>
-      </c>
-      <c r="B155" t="s">
-        <v>104</v>
-      </c>
-      <c r="C155" t="s">
-        <v>138</v>
-      </c>
-      <c r="D155" t="s">
-        <v>181</v>
-      </c>
-      <c r="E155" t="s">
-        <v>6</v>
-      </c>
-      <c r="F155" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156">
-        <v>22330051920120</v>
-      </c>
-      <c r="B156" t="s">
-        <v>104</v>
-      </c>
-      <c r="C156" t="s">
-        <v>138</v>
-      </c>
-      <c r="D156" t="s">
-        <v>181</v>
-      </c>
-      <c r="E156" t="s">
-        <v>5</v>
-      </c>
-      <c r="F156" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157">
-        <v>22330051920120</v>
-      </c>
-      <c r="B157" t="s">
-        <v>104</v>
-      </c>
-      <c r="C157" t="s">
-        <v>138</v>
-      </c>
-      <c r="D157" t="s">
-        <v>181</v>
-      </c>
-      <c r="E157" t="s">
-        <v>8</v>
-      </c>
-      <c r="F157" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158">
-        <v>22330051920122</v>
-      </c>
-      <c r="B158" t="s">
-        <v>105</v>
-      </c>
-      <c r="C158" t="s">
-        <v>139</v>
-      </c>
-      <c r="D158" t="s">
-        <v>182</v>
-      </c>
-      <c r="E158" t="s">
-        <v>9</v>
-      </c>
-      <c r="F158" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159">
-        <v>22330051920122</v>
-      </c>
-      <c r="B159" t="s">
-        <v>105</v>
-      </c>
-      <c r="C159" t="s">
-        <v>139</v>
-      </c>
-      <c r="D159" t="s">
-        <v>182</v>
-      </c>
-      <c r="E159" t="s">
-        <v>6</v>
-      </c>
-      <c r="F159" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160">
-        <v>22330051920122</v>
-      </c>
-      <c r="B160" t="s">
-        <v>105</v>
-      </c>
-      <c r="C160" t="s">
-        <v>139</v>
-      </c>
-      <c r="D160" t="s">
-        <v>182</v>
-      </c>
-      <c r="E160" t="s">
-        <v>5</v>
-      </c>
-      <c r="F160" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161">
-        <v>22330051920122</v>
-      </c>
-      <c r="B161" t="s">
-        <v>105</v>
-      </c>
-      <c r="C161" t="s">
-        <v>139</v>
-      </c>
-      <c r="D161" t="s">
-        <v>182</v>
-      </c>
-      <c r="E161" t="s">
-        <v>8</v>
-      </c>
-      <c r="F161" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="A162">
-        <v>22330051920121</v>
-      </c>
-      <c r="B162" t="s">
-        <v>106</v>
-      </c>
-      <c r="C162" t="s">
-        <v>140</v>
-      </c>
-      <c r="D162" t="s">
-        <v>183</v>
-      </c>
-      <c r="E162" t="s">
-        <v>9</v>
-      </c>
-      <c r="F162" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="A163">
-        <v>22330051920121</v>
-      </c>
-      <c r="B163" t="s">
-        <v>106</v>
-      </c>
-      <c r="C163" t="s">
-        <v>140</v>
-      </c>
-      <c r="D163" t="s">
-        <v>183</v>
-      </c>
-      <c r="E163" t="s">
-        <v>6</v>
-      </c>
-      <c r="F163" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="A164">
-        <v>22330051920121</v>
-      </c>
-      <c r="B164" t="s">
-        <v>106</v>
-      </c>
-      <c r="C164" t="s">
-        <v>140</v>
-      </c>
-      <c r="D164" t="s">
-        <v>183</v>
-      </c>
-      <c r="E164" t="s">
-        <v>5</v>
-      </c>
-      <c r="F164" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165">
-        <v>22330051920121</v>
-      </c>
-      <c r="B165" t="s">
-        <v>106</v>
-      </c>
-      <c r="C165" t="s">
-        <v>140</v>
-      </c>
-      <c r="D165" t="s">
-        <v>183</v>
-      </c>
-      <c r="E165" t="s">
-        <v>8</v>
-      </c>
-      <c r="F165" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6">
-      <c r="A166">
-        <v>22330051920123</v>
-      </c>
-      <c r="B166" t="s">
-        <v>107</v>
-      </c>
-      <c r="C166" t="s">
-        <v>141</v>
-      </c>
-      <c r="D166" t="s">
-        <v>184</v>
-      </c>
-      <c r="E166" t="s">
-        <v>9</v>
-      </c>
-      <c r="F166" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
-      <c r="A167">
-        <v>22330051920123</v>
-      </c>
-      <c r="B167" t="s">
-        <v>107</v>
-      </c>
-      <c r="C167" t="s">
-        <v>141</v>
-      </c>
-      <c r="D167" t="s">
-        <v>184</v>
-      </c>
-      <c r="E167" t="s">
-        <v>6</v>
-      </c>
-      <c r="F167" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
-      <c r="A168">
-        <v>22330051920123</v>
-      </c>
-      <c r="B168" t="s">
-        <v>107</v>
-      </c>
-      <c r="C168" t="s">
-        <v>141</v>
-      </c>
-      <c r="D168" t="s">
-        <v>184</v>
-      </c>
-      <c r="E168" t="s">
-        <v>5</v>
-      </c>
-      <c r="F168" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="A169">
-        <v>22330051920123</v>
-      </c>
-      <c r="B169" t="s">
-        <v>107</v>
-      </c>
-      <c r="C169" t="s">
-        <v>141</v>
-      </c>
-      <c r="D169" t="s">
-        <v>184</v>
-      </c>
-      <c r="E169" t="s">
-        <v>8</v>
-      </c>
-      <c r="F169" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
-      <c r="A170">
-        <v>22330051920341</v>
-      </c>
-      <c r="B170" t="s">
-        <v>108</v>
-      </c>
-      <c r="C170" t="s">
-        <v>142</v>
-      </c>
-      <c r="D170" t="s">
-        <v>185</v>
-      </c>
-      <c r="E170" t="s">
-        <v>9</v>
-      </c>
-      <c r="F170" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="A171">
-        <v>22330051920341</v>
-      </c>
-      <c r="B171" t="s">
-        <v>108</v>
-      </c>
-      <c r="C171" t="s">
-        <v>142</v>
-      </c>
-      <c r="D171" t="s">
-        <v>185</v>
-      </c>
-      <c r="E171" t="s">
-        <v>6</v>
-      </c>
-      <c r="F171" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="A172">
-        <v>22330051920341</v>
-      </c>
-      <c r="B172" t="s">
-        <v>108</v>
-      </c>
-      <c r="C172" t="s">
-        <v>142</v>
-      </c>
-      <c r="D172" t="s">
-        <v>185</v>
-      </c>
-      <c r="E172" t="s">
-        <v>5</v>
-      </c>
-      <c r="F172" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="A173">
-        <v>22330051920341</v>
-      </c>
-      <c r="B173" t="s">
-        <v>108</v>
-      </c>
-      <c r="C173" t="s">
-        <v>142</v>
-      </c>
-      <c r="D173" t="s">
-        <v>185</v>
-      </c>
-      <c r="E173" t="s">
-        <v>8</v>
-      </c>
-      <c r="F173" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -10764,7 +7336,7 @@
         <v>143</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -10781,7 +7353,7 @@
         <v>144</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -10798,7 +7370,7 @@
         <v>145</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -10815,7 +7387,7 @@
         <v>146</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -10832,7 +7404,7 @@
         <v>147</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -10849,7 +7421,7 @@
         <v>148</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -10866,7 +7438,7 @@
         <v>149</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -10883,7 +7455,7 @@
         <v>150</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -10900,7 +7472,7 @@
         <v>151</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -10917,7 +7489,7 @@
         <v>152</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -10934,7 +7506,7 @@
         <v>153</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -10951,7 +7523,7 @@
         <v>154</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -10968,7 +7540,7 @@
         <v>155</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -10985,7 +7557,7 @@
         <v>156</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -11002,7 +7574,7 @@
         <v>157</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -11019,7 +7591,7 @@
         <v>158</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -11036,7 +7608,7 @@
         <v>159</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -11053,7 +7625,7 @@
         <v>160</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -11070,7 +7642,7 @@
         <v>161</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -11087,7 +7659,7 @@
         <v>162</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -11104,7 +7676,7 @@
         <v>163</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -11121,7 +7693,7 @@
         <v>164</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -11138,7 +7710,7 @@
         <v>165</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -11155,7 +7727,7 @@
         <v>166</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -11172,7 +7744,7 @@
         <v>167</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -11189,7 +7761,7 @@
         <v>168</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -11206,7 +7778,7 @@
         <v>169</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -11223,7 +7795,7 @@
         <v>170</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -11240,7 +7812,7 @@
         <v>171</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -11257,7 +7829,7 @@
         <v>172</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -11274,7 +7846,7 @@
         <v>173</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -11291,7 +7863,7 @@
         <v>174</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -11308,7 +7880,7 @@
         <v>175</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -11325,7 +7897,7 @@
         <v>176</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -11342,7 +7914,7 @@
         <v>177</v>
       </c>
       <c r="E36">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -11359,7 +7931,7 @@
         <v>178</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -11376,7 +7948,7 @@
         <v>179</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -11393,7 +7965,7 @@
         <v>180</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -11410,7 +7982,7 @@
         <v>181</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -11427,7 +7999,7 @@
         <v>182</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -11444,7 +8016,7 @@
         <v>183</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -11461,7 +8033,7 @@
         <v>184</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -11478,7 +8050,7 @@
         <v>185</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11488,7 +8060,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -11518,6 +8090,190 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920340</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920340</v>
+      </c>
+      <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920100</v>
+      </c>
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920100</v>
+      </c>
+      <c r="B5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920087</v>
+      </c>
+      <c r="B6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920339</v>
+      </c>
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920114</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920121</v>
+      </c>
+      <c r="B9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/2ALCM - Estadisticos 20222.xlsx
+++ b/grupos/2ALCM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="189">
   <si>
     <t>Materia</t>
   </si>
@@ -222,10 +222,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>NC</t>
@@ -7102,7 +7111,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3">
         <v>43</v>
@@ -7134,7 +7143,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>43</v>
@@ -7166,7 +7175,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C5">
         <v>43</v>
@@ -7198,7 +7207,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C6">
         <v>43</v>
@@ -7230,7 +7239,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C7">
         <v>43</v>
@@ -7273,16 +7282,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -7307,16 +7316,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>65</v>
@@ -7327,13 +7336,13 @@
         <v>22330051920086</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -7344,13 +7353,13 @@
         <v>22330051920085</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -7361,13 +7370,13 @@
         <v>22330051920087</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -7378,13 +7387,13 @@
         <v>22330051920337</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -7395,13 +7404,13 @@
         <v>22330051920090</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -7412,13 +7421,13 @@
         <v>22330051920091</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7429,13 +7438,13 @@
         <v>22330051920092</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -7446,13 +7455,13 @@
         <v>22330051920338</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -7463,13 +7472,13 @@
         <v>22330051920093</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -7480,13 +7489,13 @@
         <v>22330051920094</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -7497,13 +7506,13 @@
         <v>22330051920095</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -7514,13 +7523,13 @@
         <v>22330051920096</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -7531,13 +7540,13 @@
         <v>22330051920097</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -7548,13 +7557,13 @@
         <v>22330051920098</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -7565,13 +7574,13 @@
         <v>22330051920339</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -7582,13 +7591,13 @@
         <v>22330051920088</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -7599,13 +7608,13 @@
         <v>22330051920340</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -7616,13 +7625,13 @@
         <v>22330051920099</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -7633,13 +7642,13 @@
         <v>22330051920100</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -7650,13 +7659,13 @@
         <v>22330051920101</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -7667,13 +7676,13 @@
         <v>22330051920089</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -7684,13 +7693,13 @@
         <v>22330051920102</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -7701,13 +7710,13 @@
         <v>22330051920103</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -7718,13 +7727,13 @@
         <v>22330051920105</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -7735,13 +7744,13 @@
         <v>22330051920104</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -7752,13 +7761,13 @@
         <v>22330051920106</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -7769,13 +7778,13 @@
         <v>22330051920108</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -7786,13 +7795,13 @@
         <v>22330051920107</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D29" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -7803,13 +7812,13 @@
         <v>22330051920109</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D30" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -7820,13 +7829,13 @@
         <v>22330051920111</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D31" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -7837,13 +7846,13 @@
         <v>22330051920112</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -7854,13 +7863,13 @@
         <v>22330051920113</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D33" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -7871,13 +7880,13 @@
         <v>22330051920114</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -7888,13 +7897,13 @@
         <v>22330051920115</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D35" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -7905,13 +7914,13 @@
         <v>22330051920117</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -7922,13 +7931,13 @@
         <v>22330051920118</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D37" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -7939,13 +7948,13 @@
         <v>22330051920116</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D38" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -7956,13 +7965,13 @@
         <v>22330051920119</v>
       </c>
       <c r="B39" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C39" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D39" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -7973,13 +7982,13 @@
         <v>22330051920120</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D40" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -7990,13 +7999,13 @@
         <v>22330051920122</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D41" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -8007,13 +8016,13 @@
         <v>22330051920121</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D42" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -8024,13 +8033,13 @@
         <v>22330051920123</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D43" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -8041,13 +8050,13 @@
         <v>22330051920341</v>
       </c>
       <c r="B44" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C44" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D44" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -8069,16 +8078,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -8095,13 +8104,13 @@
         <v>22330051920340</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -8118,19 +8127,19 @@
         <v>22330051920340</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -8141,13 +8150,13 @@
         <v>22330051920100</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -8164,19 +8173,19 @@
         <v>22330051920100</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -8187,19 +8196,19 @@
         <v>22330051920087</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -8210,13 +8219,13 @@
         <v>22330051920339</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -8233,19 +8242,19 @@
         <v>22330051920114</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -8256,19 +8265,19 @@
         <v>22330051920121</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9">
         <v>5</v>

--- a/grupos/2ALCM - Estadisticos 20222.xlsx
+++ b/grupos/2ALCM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -249,349 +248,58 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>JALAPA</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
-    <t>LOMAN</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
+    <t>TELE</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>LUGO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>SHEIKH</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>AGUIRRE</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>LUGO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>FALFAN</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ONOFRE</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>BAZAN</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>CUAHUA</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>OYOLA</t>
-  </si>
-  <si>
-    <t>SAAVEDRA</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>IRAIS</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>DAMON</t>
-  </si>
-  <si>
-    <t>AYLIN VALENTINA</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>MIRIAM ANELI</t>
-  </si>
-  <si>
-    <t>HEIDY IDARA</t>
-  </si>
-  <si>
-    <t>MARLEN FERNANDA</t>
-  </si>
-  <si>
-    <t>AMERICA</t>
-  </si>
-  <si>
-    <t>LINDA PAOLA</t>
-  </si>
-  <si>
-    <t>MARIO</t>
-  </si>
-  <si>
     <t>MARCO</t>
   </si>
   <si>
-    <t>ANETTE</t>
+    <t>ZAYRA</t>
   </si>
   <si>
     <t>JAZMIN</t>
   </si>
   <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>ALEJANDRA JANETTE</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>ESMERALDA AIMEE</t>
-  </si>
-  <si>
-    <t>ELISA MARELI</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>JESUA JEHIELI</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>BARUCH BOSET</t>
-  </si>
-  <si>
-    <t>AHILY</t>
-  </si>
-  <si>
-    <t>MAYTE</t>
-  </si>
-  <si>
-    <t>YUSEF ABRIL</t>
-  </si>
-  <si>
-    <t>BETZABE</t>
-  </si>
-  <si>
-    <t>ILSE LEILANI</t>
-  </si>
-  <si>
     <t>ILEANA</t>
   </si>
   <si>
-    <t>IAN YASSEL</t>
-  </si>
-  <si>
-    <t>DANA DANIELA</t>
-  </si>
-  <si>
-    <t>VICTORIA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>IVON</t>
-  </si>
-  <si>
-    <t>TANIA REYNA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
     <t>BETSABETH</t>
-  </si>
-  <si>
-    <t>JOSELYN</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -644,11 +352,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1104,7 +813,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1181,7 +890,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1258,7 +967,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1294,7 +1003,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1335,7 +1044,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1412,7 +1121,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1448,7 +1157,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1489,7 +1198,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1525,7 +1234,7 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1566,7 +1275,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1643,7 +1352,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1720,7 +1429,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1797,7 +1506,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1874,7 +1583,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1951,7 +1660,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1987,7 +1696,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2028,7 +1737,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2105,7 +1814,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2182,7 +1891,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2218,7 +1927,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2259,7 +1968,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2295,7 +2004,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2336,7 +2045,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2372,7 +2081,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2413,7 +2122,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2449,7 +2158,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2490,7 +2199,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2526,7 +2235,7 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2567,7 +2276,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2644,7 +2353,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2680,7 +2389,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2721,7 +2430,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2798,7 +2507,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2875,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2952,7 +2661,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2988,7 +2697,7 @@
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -3029,7 +2738,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3106,7 +2815,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3142,7 +2851,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3183,7 +2892,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3219,7 +2928,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3260,7 +2969,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3337,7 +3046,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3414,7 +3123,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3491,7 +3200,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3527,7 +3236,7 @@
         <v>7</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3568,7 +3277,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3645,7 +3354,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3681,7 +3390,7 @@
         <v>9</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3722,7 +3431,7 @@
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3799,7 +3508,7 @@
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3876,7 +3585,7 @@
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3912,7 +3621,7 @@
         <v>7</v>
       </c>
       <c r="Y40">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3953,7 +3662,7 @@
         <v>-1</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -4030,7 +3739,7 @@
         <v>-1</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4107,7 +3816,7 @@
         <v>-1</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4143,7 +3852,7 @@
         <v>6</v>
       </c>
       <c r="Y43">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4184,7 +3893,7 @@
         <v>-1</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -4220,7 +3929,7 @@
         <v>7</v>
       </c>
       <c r="Y44">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4261,7 +3970,7 @@
         <v>-1</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -4338,7 +4047,7 @@
         <v>-1</v>
       </c>
       <c r="M46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N46">
         <v>-1</v>
@@ -4525,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>116.7</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -4584,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -4643,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -4702,7 +4411,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>111.7</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -4761,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -4820,7 +4529,7 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -4879,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>116.7</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -4938,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -4997,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -5056,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -5115,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -5174,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>116.7</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -5233,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>116.7</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5292,7 +5001,7 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5351,7 +5060,7 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -5410,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -5469,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -5528,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -5587,7 +5296,7 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -5646,7 +5355,7 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -5705,7 +5414,7 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -5764,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -5823,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -5882,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -5941,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -6000,7 +5709,7 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -6059,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -6118,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>101.7</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -6177,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -6236,7 +5945,7 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -6295,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -6354,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -6413,7 +6122,7 @@
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>116.7</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -6472,7 +6181,7 @@
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -6531,7 +6240,7 @@
         <v>0</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>111.7</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -6590,7 +6299,7 @@
         <v>0</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -6649,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>113.3</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -6708,7 +6417,7 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>116.7</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -6767,7 +6476,7 @@
         <v>0</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N42">
         <v>0</v>
@@ -6826,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>108.3</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -6885,7 +6594,7 @@
         <v>0</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>116.7</v>
       </c>
       <c r="N44">
         <v>0</v>
@@ -6944,7 +6653,7 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>116.7</v>
       </c>
       <c r="N45">
         <v>0</v>
@@ -7003,7 +6712,7 @@
         <v>0</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N46">
         <v>0</v>
@@ -7040,6 +6749,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -7090,11 +6801,11 @@
       <c r="E2">
         <v>6</v>
       </c>
-      <c r="F2">
-        <v>86.05</v>
-      </c>
-      <c r="G2">
-        <v>13.95</v>
+      <c r="F2" s="2">
+        <v>86</v>
+      </c>
+      <c r="G2" s="2">
+        <v>14</v>
       </c>
       <c r="H2">
         <v>7.3</v>
@@ -7102,7 +6813,7 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7122,19 +6833,19 @@
       <c r="E3">
         <v>6</v>
       </c>
-      <c r="F3">
-        <v>86.05</v>
-      </c>
-      <c r="G3">
-        <v>13.95</v>
+      <c r="F3" s="2">
+        <v>86</v>
+      </c>
+      <c r="G3" s="2">
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7154,11 +6865,11 @@
       <c r="E4">
         <v>5</v>
       </c>
-      <c r="F4">
-        <v>88.37</v>
-      </c>
-      <c r="G4">
-        <v>11.63</v>
+      <c r="F4" s="2">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="G4" s="2">
+        <v>11.6</v>
       </c>
       <c r="H4">
         <v>8.6</v>
@@ -7166,7 +6877,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7186,10 +6897,10 @@
       <c r="E5">
         <v>4</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>90.7</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>9.300000000000001</v>
       </c>
       <c r="H5">
@@ -7198,7 +6909,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7218,11 +6929,11 @@
       <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6">
-        <v>93.02</v>
-      </c>
-      <c r="G6">
-        <v>6.98</v>
+      <c r="F6" s="2">
+        <v>93</v>
+      </c>
+      <c r="G6" s="2">
+        <v>7</v>
       </c>
       <c r="H6">
         <v>8.4</v>
@@ -7230,7 +6941,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7250,11 +6961,11 @@
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7">
-        <v>97.67</v>
-      </c>
-      <c r="G7">
-        <v>2.33</v>
+      <c r="F7" s="2">
+        <v>97.7</v>
+      </c>
+      <c r="G7" s="2">
+        <v>2.3</v>
       </c>
       <c r="H7">
         <v>8.6</v>
@@ -7262,7 +6973,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7307,769 +7018,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E44"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>22330051920086</v>
-      </c>
-      <c r="B2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>22330051920085</v>
-      </c>
-      <c r="B3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>22330051920087</v>
-      </c>
-      <c r="B4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" t="s">
-        <v>148</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>22330051920337</v>
-      </c>
-      <c r="B5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>22330051920090</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>22330051920091</v>
-      </c>
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>22330051920092</v>
-      </c>
-      <c r="B8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D8" t="s">
-        <v>152</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>22330051920338</v>
-      </c>
-      <c r="B9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>22330051920093</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" t="s">
-        <v>154</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>22330051920094</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>22330051920095</v>
-      </c>
-      <c r="B12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>22330051920096</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" t="s">
-        <v>157</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>22330051920097</v>
-      </c>
-      <c r="B14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D14" t="s">
-        <v>158</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>22330051920098</v>
-      </c>
-      <c r="B15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>22330051920339</v>
-      </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" t="s">
-        <v>160</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>22330051920088</v>
-      </c>
-      <c r="B17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" t="s">
-        <v>123</v>
-      </c>
-      <c r="D17" t="s">
-        <v>161</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>22330051920340</v>
-      </c>
-      <c r="B18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" t="s">
-        <v>162</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>22330051920099</v>
-      </c>
-      <c r="B19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" t="s">
-        <v>163</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>22330051920100</v>
-      </c>
-      <c r="B20" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" t="s">
-        <v>125</v>
-      </c>
-      <c r="D20" t="s">
-        <v>164</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>22330051920101</v>
-      </c>
-      <c r="B21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>165</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>22330051920089</v>
-      </c>
-      <c r="B22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" t="s">
-        <v>126</v>
-      </c>
-      <c r="D22" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>22330051920102</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>127</v>
-      </c>
-      <c r="D23" t="s">
-        <v>167</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>22330051920103</v>
-      </c>
-      <c r="B24" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" t="s">
-        <v>128</v>
-      </c>
-      <c r="D24" t="s">
-        <v>168</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>22330051920105</v>
-      </c>
-      <c r="B25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25" t="s">
-        <v>169</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>22330051920104</v>
-      </c>
-      <c r="B26" t="s">
-        <v>94</v>
-      </c>
-      <c r="C26" t="s">
-        <v>130</v>
-      </c>
-      <c r="D26" t="s">
-        <v>170</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>22330051920106</v>
-      </c>
-      <c r="B27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" t="s">
-        <v>131</v>
-      </c>
-      <c r="D27" t="s">
-        <v>171</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>22330051920108</v>
-      </c>
-      <c r="B28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C28" t="s">
-        <v>102</v>
-      </c>
-      <c r="D28" t="s">
-        <v>172</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>22330051920107</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" t="s">
-        <v>129</v>
-      </c>
-      <c r="D29" t="s">
-        <v>173</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>22330051920109</v>
-      </c>
-      <c r="B30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" t="s">
-        <v>174</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>22330051920111</v>
-      </c>
-      <c r="B31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C31" t="s">
-        <v>133</v>
-      </c>
-      <c r="D31" t="s">
-        <v>175</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>22330051920112</v>
-      </c>
-      <c r="B32" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" t="s">
-        <v>106</v>
-      </c>
-      <c r="D32" t="s">
-        <v>176</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>22330051920113</v>
-      </c>
-      <c r="B33" t="s">
-        <v>100</v>
-      </c>
-      <c r="C33" t="s">
-        <v>134</v>
-      </c>
-      <c r="D33" t="s">
-        <v>177</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>22330051920114</v>
-      </c>
-      <c r="B34" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" t="s">
-        <v>135</v>
-      </c>
-      <c r="D34" t="s">
-        <v>178</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>22330051920115</v>
-      </c>
-      <c r="B35" t="s">
-        <v>102</v>
-      </c>
-      <c r="C35" t="s">
-        <v>136</v>
-      </c>
-      <c r="D35" t="s">
-        <v>179</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>22330051920117</v>
-      </c>
-      <c r="B36" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" t="s">
-        <v>137</v>
-      </c>
-      <c r="D36" t="s">
-        <v>180</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
-        <v>22330051920118</v>
-      </c>
-      <c r="B37" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" t="s">
-        <v>138</v>
-      </c>
-      <c r="D37" t="s">
-        <v>181</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>22330051920116</v>
-      </c>
-      <c r="B38" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" t="s">
-        <v>139</v>
-      </c>
-      <c r="D38" t="s">
-        <v>182</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39">
-        <v>22330051920119</v>
-      </c>
-      <c r="B39" t="s">
-        <v>106</v>
-      </c>
-      <c r="C39" t="s">
-        <v>140</v>
-      </c>
-      <c r="D39" t="s">
-        <v>183</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40">
-        <v>22330051920120</v>
-      </c>
-      <c r="B40" t="s">
-        <v>107</v>
-      </c>
-      <c r="C40" t="s">
-        <v>141</v>
-      </c>
-      <c r="D40" t="s">
-        <v>184</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41">
-        <v>22330051920122</v>
-      </c>
-      <c r="B41" t="s">
-        <v>108</v>
-      </c>
-      <c r="C41" t="s">
-        <v>142</v>
-      </c>
-      <c r="D41" t="s">
-        <v>185</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42">
-        <v>22330051920121</v>
-      </c>
-      <c r="B42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C42" t="s">
-        <v>143</v>
-      </c>
-      <c r="D42" t="s">
-        <v>186</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43">
-        <v>22330051920123</v>
-      </c>
-      <c r="B43" t="s">
-        <v>110</v>
-      </c>
-      <c r="C43" t="s">
-        <v>144</v>
-      </c>
-      <c r="D43" t="s">
-        <v>187</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44">
-        <v>22330051920341</v>
-      </c>
-      <c r="B44" t="s">
-        <v>111</v>
-      </c>
-      <c r="C44" t="s">
-        <v>145</v>
-      </c>
-      <c r="D44" t="s">
-        <v>188</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8101,22 +7050,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920340</v>
+        <v>22330051920097</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8124,22 +7073,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920340</v>
+        <v>22330051920097</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -8150,13 +7099,13 @@
         <v>22330051920100</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>164</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -8173,13 +7122,13 @@
         <v>22330051920100</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -8193,22 +7142,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920087</v>
+        <v>22330051920339</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -8216,22 +7165,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920339</v>
+        <v>22330051920114</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -8239,47 +7188,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920114</v>
+        <v>22330051920121</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920121</v>
-      </c>
-      <c r="B9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" t="s">
-        <v>143</v>
-      </c>
-      <c r="D9" t="s">
-        <v>186</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ALCM - Estadisticos 20222.xlsx
+++ b/grupos/2ALCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -227,15 +227,15 @@
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -248,12 +248,15 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>JALAPA</t>
   </si>
   <si>
@@ -263,12 +266,15 @@
     <t>TELE</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>LUGO</t>
+  </si>
+  <si>
     <t>ESPIRITU</t>
   </si>
   <si>
-    <t>LUGO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -278,10 +284,13 @@
     <t>HUERTA</t>
   </si>
   <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
     <t>MARCO</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
   </si>
   <si>
     <t>JAZMIN</t>
@@ -801,16 +810,16 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>9</v>
@@ -878,16 +887,16 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>9</v>
@@ -923,7 +932,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>9</v>
@@ -955,16 +964,16 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>7</v>
@@ -994,7 +1003,7 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1032,16 +1041,16 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>5</v>
@@ -1109,16 +1118,16 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>6</v>
@@ -1145,10 +1154,10 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1186,16 +1195,16 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>9</v>
@@ -1222,7 +1231,7 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>10</v>
@@ -1263,16 +1272,16 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1340,16 +1349,16 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>8</v>
@@ -1417,16 +1426,16 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
         <v>9</v>
@@ -1494,16 +1503,16 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
         <v>8</v>
@@ -1533,7 +1542,7 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1571,16 +1580,16 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -1616,7 +1625,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1648,16 +1657,16 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -1684,7 +1693,7 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>10</v>
@@ -1693,7 +1702,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1725,16 +1734,16 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>8</v>
@@ -1770,7 +1779,7 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1802,16 +1811,16 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>9</v>
@@ -1841,7 +1850,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -1879,16 +1888,16 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>8</v>
@@ -1915,16 +1924,16 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>5</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -1956,16 +1965,16 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>9</v>
@@ -1992,10 +2001,10 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2033,16 +2042,16 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>4</v>
@@ -2110,16 +2119,16 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>5</v>
@@ -2149,13 +2158,13 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>8</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2187,16 +2196,16 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -2226,7 +2235,7 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2264,16 +2273,16 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>3</v>
@@ -2341,16 +2350,16 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -2418,16 +2427,16 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>10</v>
@@ -2463,7 +2472,7 @@
         <v>10</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2495,16 +2504,16 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>8</v>
@@ -2540,7 +2549,7 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2572,16 +2581,16 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -2649,16 +2658,16 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>4</v>
@@ -2685,10 +2694,10 @@
         <v>5</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2726,16 +2735,16 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>9</v>
@@ -2762,7 +2771,7 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>10</v>
@@ -2803,16 +2812,16 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
         <v>8</v>
@@ -2839,10 +2848,10 @@
         <v>6</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -2880,16 +2889,16 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>5</v>
@@ -2916,16 +2925,16 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>8</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -2957,16 +2966,16 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>9</v>
@@ -2993,7 +3002,7 @@
         <v>8</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3034,16 +3043,16 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>9</v>
@@ -3111,16 +3120,16 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
         <v>9</v>
@@ -3150,7 +3159,7 @@
         <v>9</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>9</v>
@@ -3188,16 +3197,16 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
         <v>6</v>
@@ -3224,7 +3233,7 @@
         <v>7</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -3265,16 +3274,16 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M36">
         <v>6</v>
@@ -3342,16 +3351,16 @@
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M37">
         <v>7</v>
@@ -3378,7 +3387,7 @@
         <v>8</v>
       </c>
       <c r="U37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V37">
         <v>10</v>
@@ -3419,16 +3428,16 @@
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K38">
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M38">
         <v>6</v>
@@ -3455,16 +3464,16 @@
         <v>5</v>
       </c>
       <c r="U38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W38">
         <v>5</v>
       </c>
       <c r="X38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>5</v>
@@ -3496,16 +3505,16 @@
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K39">
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
         <v>10</v>
@@ -3573,16 +3582,16 @@
         <v>-1</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K40">
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M40">
         <v>8</v>
@@ -3650,16 +3659,16 @@
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K41">
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M41">
         <v>9</v>
@@ -3689,7 +3698,7 @@
         <v>6</v>
       </c>
       <c r="V41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W41">
         <v>9</v>
@@ -3727,16 +3736,16 @@
         <v>-1</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K42">
         <v>-1</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M42">
         <v>10</v>
@@ -3804,16 +3813,16 @@
         <v>-1</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K43">
         <v>-1</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M43">
         <v>6</v>
@@ -3843,13 +3852,13 @@
         <v>8</v>
       </c>
       <c r="V43">
+        <v>8</v>
+      </c>
+      <c r="W43">
+        <v>8</v>
+      </c>
+      <c r="X43">
         <v>5</v>
-      </c>
-      <c r="W43">
-        <v>8</v>
-      </c>
-      <c r="X43">
-        <v>6</v>
       </c>
       <c r="Y43">
         <v>8</v>
@@ -3881,16 +3890,16 @@
         <v>-1</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K44">
         <v>-1</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M44">
         <v>6</v>
@@ -3917,10 +3926,10 @@
         <v>6</v>
       </c>
       <c r="U44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V44">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W44">
         <v>9</v>
@@ -3958,16 +3967,16 @@
         <v>-1</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K45">
         <v>-1</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M45">
         <v>9</v>
@@ -4035,16 +4044,16 @@
         <v>-1</v>
       </c>
       <c r="I46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K46">
         <v>-1</v>
       </c>
       <c r="L46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M46">
         <v>10</v>
@@ -4222,16 +4231,16 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
         <v>116.7</v>
@@ -4281,16 +4290,16 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M5">
         <v>120</v>
@@ -4340,16 +4349,16 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
         <v>120</v>
@@ -4399,16 +4408,16 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M7">
         <v>111.7</v>
@@ -4458,16 +4467,16 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M8">
         <v>120</v>
@@ -4517,16 +4526,16 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M9">
         <v>120</v>
@@ -4576,16 +4585,16 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
         <v>116.7</v>
@@ -4635,16 +4644,16 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>120</v>
@@ -4694,16 +4703,16 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
         <v>120</v>
@@ -4753,16 +4762,16 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
         <v>120</v>
@@ -4812,16 +4821,16 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14">
         <v>120</v>
@@ -4871,16 +4880,16 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15">
         <v>116.7</v>
@@ -4930,16 +4939,16 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16">
         <v>116.7</v>
@@ -4989,16 +4998,16 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17">
         <v>120</v>
@@ -5048,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
         <v>120</v>
@@ -5107,16 +5116,16 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
         <v>120</v>
@@ -5166,16 +5175,16 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M20">
         <v>115</v>
@@ -5225,16 +5234,16 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
         <v>120</v>
@@ -5284,16 +5293,16 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
         <v>120</v>
@@ -5343,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M23">
         <v>95</v>
@@ -5402,16 +5411,16 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
         <v>120</v>
@@ -5461,16 +5470,16 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
         <v>120</v>
@@ -5520,16 +5529,16 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M26">
         <v>120</v>
@@ -5579,16 +5588,16 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
         <v>120</v>
@@ -5638,16 +5647,16 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M28">
         <v>113.3</v>
@@ -5697,16 +5706,16 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29">
         <v>120</v>
@@ -5756,16 +5765,16 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M30">
         <v>113.3</v>
@@ -5815,16 +5824,16 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M31">
         <v>101.7</v>
@@ -5874,16 +5883,16 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
         <v>120</v>
@@ -5933,16 +5942,16 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33">
         <v>120</v>
@@ -5992,16 +6001,16 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34">
         <v>120</v>
@@ -6051,16 +6060,16 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35">
         <v>120</v>
@@ -6110,16 +6119,16 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M36">
         <v>116.7</v>
@@ -6169,16 +6178,16 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M37">
         <v>120</v>
@@ -6228,16 +6237,16 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M38">
         <v>111.7</v>
@@ -6287,16 +6296,16 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39">
         <v>120</v>
@@ -6346,16 +6355,16 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M40">
         <v>113.3</v>
@@ -6405,16 +6414,16 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41">
         <v>116.7</v>
@@ -6464,16 +6473,16 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M42">
         <v>120</v>
@@ -6523,16 +6532,16 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K43">
         <v>0</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M43">
         <v>108.3</v>
@@ -6582,16 +6591,16 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M44">
         <v>116.7</v>
@@ -6641,16 +6650,16 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M45">
         <v>116.7</v>
@@ -6700,16 +6709,16 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M46">
         <v>120</v>
@@ -6851,7 +6860,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
@@ -6860,19 +6869,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>88.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="G4" s="2">
-        <v>11.6</v>
+        <v>7</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6883,28 +6892,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5">
         <v>43</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>90.7</v>
+        <v>93</v>
       </c>
       <c r="G5" s="2">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6915,7 +6924,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
@@ -6924,19 +6933,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>93</v>
+        <v>95.3</v>
       </c>
       <c r="G6" s="2">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6947,7 +6956,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -6968,7 +6977,7 @@
         <v>2.3</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7018,7 +7027,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7050,22 +7059,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920097</v>
+        <v>22330051920340</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7073,22 +7082,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920097</v>
+        <v>22330051920340</v>
       </c>
       <c r="B3" t="s">
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7102,10 +7111,10 @@
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -7125,10 +7134,10 @@
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -7142,22 +7151,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920339</v>
+        <v>22330051920097</v>
       </c>
       <c r="B6" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7165,22 +7174,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920114</v>
+        <v>22330051920339</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7188,24 +7197,47 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920121</v>
+        <v>22330051920114</v>
       </c>
       <c r="B8" t="s">
         <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920121</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
         <v>69</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ALCM - Estadisticos 20222.xlsx
+++ b/grupos/2ALCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="88">
   <si>
     <t>Materia</t>
   </si>
@@ -251,12 +251,6 @@
     <t>LARRACILLA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>JALAPA</t>
   </si>
   <si>
@@ -269,12 +263,6 @@
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>LUGO</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -285,12 +273,6 @@
   </si>
   <si>
     <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>MARCO</t>
   </si>
   <si>
     <t>JAZMIN</t>
@@ -816,7 +798,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -893,7 +875,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -970,7 +952,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -1006,7 +988,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1047,7 +1029,7 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1124,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>7</v>
@@ -1201,7 +1183,7 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>8</v>
@@ -1278,7 +1260,7 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>9</v>
@@ -1355,7 +1337,7 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -1432,7 +1414,7 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -1509,7 +1491,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>7</v>
@@ -1586,7 +1568,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>7</v>
@@ -1663,7 +1645,7 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>8</v>
@@ -1740,7 +1722,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>8</v>
@@ -1776,7 +1758,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -1817,7 +1799,7 @@
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>8</v>
@@ -1894,7 +1876,7 @@
         <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>8</v>
@@ -1930,7 +1912,7 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -1971,7 +1953,7 @@
         <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -2048,7 +2030,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -2084,7 +2066,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2125,7 +2107,7 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>7</v>
@@ -2161,7 +2143,7 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2202,7 +2184,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>8</v>
@@ -2279,7 +2261,7 @@
         <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -2315,7 +2297,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>6</v>
@@ -2356,7 +2338,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>8</v>
@@ -2392,7 +2374,7 @@
         <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>8</v>
@@ -2433,7 +2415,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2510,7 +2492,7 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -2546,7 +2528,7 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2587,7 +2569,7 @@
         <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -2664,7 +2646,7 @@
         <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>6</v>
@@ -2741,7 +2723,7 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>9</v>
@@ -2818,7 +2800,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
         <v>7</v>
@@ -2895,7 +2877,7 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -2972,7 +2954,7 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>8</v>
@@ -3049,7 +3031,7 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -3126,7 +3108,7 @@
         <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
         <v>7</v>
@@ -3162,7 +3144,7 @@
         <v>9</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>8</v>
@@ -3203,7 +3185,7 @@
         <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L35">
         <v>7</v>
@@ -3239,7 +3221,7 @@
         <v>10</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -3280,7 +3262,7 @@
         <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L36">
         <v>7</v>
@@ -3357,7 +3339,7 @@
         <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
         <v>8</v>
@@ -3393,7 +3375,7 @@
         <v>10</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>9</v>
@@ -3434,7 +3416,7 @@
         <v>7</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L38">
         <v>7</v>
@@ -3511,7 +3493,7 @@
         <v>10</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
         <v>10</v>
@@ -3588,7 +3570,7 @@
         <v>10</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L40">
         <v>7</v>
@@ -3624,7 +3606,7 @@
         <v>10</v>
       </c>
       <c r="W40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>7</v>
@@ -3665,7 +3647,7 @@
         <v>10</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L41">
         <v>7</v>
@@ -3701,7 +3683,7 @@
         <v>10</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X41">
         <v>7</v>
@@ -3742,7 +3724,7 @@
         <v>10</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
         <v>10</v>
@@ -3819,7 +3801,7 @@
         <v>10</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L43">
         <v>5</v>
@@ -3855,7 +3837,7 @@
         <v>8</v>
       </c>
       <c r="W43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X43">
         <v>5</v>
@@ -3896,7 +3878,7 @@
         <v>10</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L44">
         <v>7</v>
@@ -3973,7 +3955,7 @@
         <v>10</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L45">
         <v>7</v>
@@ -4050,7 +4032,7 @@
         <v>10</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L46">
         <v>10</v>
@@ -4237,7 +4219,7 @@
         <v>105</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -4296,7 +4278,7 @@
         <v>110</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>95</v>
@@ -4355,7 +4337,7 @@
         <v>110</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -4414,7 +4396,7 @@
         <v>95</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L7">
         <v>80</v>
@@ -4473,7 +4455,7 @@
         <v>110</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>95</v>
@@ -4532,7 +4514,7 @@
         <v>110</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>95</v>
@@ -4591,7 +4573,7 @@
         <v>110</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -4650,7 +4632,7 @@
         <v>110</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -4709,7 +4691,7 @@
         <v>110</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -4768,7 +4750,7 @@
         <v>110</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -4827,7 +4809,7 @@
         <v>110</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4886,7 +4868,7 @@
         <v>105</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -4945,7 +4927,7 @@
         <v>110</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -5004,7 +4986,7 @@
         <v>110</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -5063,7 +5045,7 @@
         <v>105</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -5122,7 +5104,7 @@
         <v>110</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -5181,7 +5163,7 @@
         <v>105</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>90</v>
@@ -5240,7 +5222,7 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -5299,7 +5281,7 @@
         <v>110</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -5358,7 +5340,7 @@
         <v>85</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L23">
         <v>90</v>
@@ -5417,7 +5399,7 @@
         <v>110</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -5476,7 +5458,7 @@
         <v>110</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -5535,7 +5517,7 @@
         <v>105</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>95</v>
@@ -5594,7 +5576,7 @@
         <v>110</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -5653,7 +5635,7 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L28">
         <v>80</v>
@@ -5712,7 +5694,7 @@
         <v>105</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -5771,7 +5753,7 @@
         <v>105</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="L30">
         <v>95</v>
@@ -5830,7 +5812,7 @@
         <v>110</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="L31">
         <v>95</v>
@@ -5889,7 +5871,7 @@
         <v>110</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -5948,7 +5930,7 @@
         <v>110</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -6007,7 +5989,7 @@
         <v>110</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -6066,7 +6048,7 @@
         <v>105</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -6125,7 +6107,7 @@
         <v>95</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36">
         <v>100</v>
@@ -6184,7 +6166,7 @@
         <v>110</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L37">
         <v>100</v>
@@ -6243,7 +6225,7 @@
         <v>85</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L38">
         <v>95</v>
@@ -6302,7 +6284,7 @@
         <v>110</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L39">
         <v>100</v>
@@ -6361,7 +6343,7 @@
         <v>105</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L40">
         <v>95</v>
@@ -6420,7 +6402,7 @@
         <v>110</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L41">
         <v>100</v>
@@ -6479,7 +6461,7 @@
         <v>110</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L42">
         <v>100</v>
@@ -6538,7 +6520,7 @@
         <v>90</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L43">
         <v>80</v>
@@ -6597,7 +6579,7 @@
         <v>110</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L44">
         <v>100</v>
@@ -6656,7 +6638,7 @@
         <v>105</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L45">
         <v>100</v>
@@ -6715,7 +6697,7 @@
         <v>110</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L46">
         <v>100</v>
@@ -6913,7 +6895,7 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7027,7 +7009,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7065,10 +7047,10 @@
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -7088,10 +7070,10 @@
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -7105,16 +7087,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920100</v>
+        <v>22330051920339</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -7128,16 +7110,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920100</v>
+        <v>22330051920114</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -7151,93 +7133,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920097</v>
+        <v>22330051920121</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>69</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920339</v>
-      </c>
-      <c r="B7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920114</v>
-      </c>
-      <c r="B8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920121</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ALCM - Estadisticos 20222.xlsx
+++ b/grupos/2ALCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -254,9 +254,15 @@
     <t>JALAPA</t>
   </si>
   <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
     <t>TELE</t>
   </si>
   <si>
@@ -266,9 +272,15 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
+    <t>GIL</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
@@ -278,7 +290,13 @@
     <t>JAZMIN</t>
   </si>
   <si>
+    <t>AHILY</t>
+  </si>
+  <si>
     <t>ILEANA</t>
+  </si>
+  <si>
+    <t>JESUS</t>
   </si>
   <si>
     <t>BETSABETH</t>
@@ -789,7 +807,7 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>10</v>
@@ -825,7 +843,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -866,7 +884,7 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>10</v>
@@ -902,7 +920,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -943,7 +961,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>9</v>
@@ -979,7 +997,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>10</v>
@@ -1020,7 +1038,7 @@
         <v>3</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>5</v>
@@ -1097,7 +1115,7 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>7</v>
@@ -1133,7 +1151,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1174,7 +1192,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -1210,7 +1228,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1251,7 +1269,7 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>10</v>
@@ -1287,7 +1305,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>10</v>
@@ -1328,7 +1346,7 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>10</v>
@@ -1364,7 +1382,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1405,7 +1423,7 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>9</v>
@@ -1441,7 +1459,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>10</v>
@@ -1482,7 +1500,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>9</v>
@@ -1518,7 +1536,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1559,7 +1577,7 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>10</v>
@@ -1595,7 +1613,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -1636,7 +1654,7 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>8</v>
@@ -1672,7 +1690,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1713,7 +1731,7 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <v>9</v>
@@ -1790,7 +1808,7 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>10</v>
@@ -1826,7 +1844,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -1867,7 +1885,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -1944,7 +1962,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>9</v>
@@ -2021,7 +2039,7 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>6</v>
@@ -2098,7 +2116,7 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>6</v>
@@ -2175,7 +2193,7 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
         <v>9</v>
@@ -2252,7 +2270,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>6</v>
@@ -2329,7 +2347,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>10</v>
@@ -2365,7 +2383,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2406,7 +2424,7 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
         <v>10</v>
@@ -2483,7 +2501,7 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <v>9</v>
@@ -2519,7 +2537,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>9</v>
@@ -2560,7 +2578,7 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>10</v>
@@ -2637,7 +2655,7 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>5</v>
@@ -2714,7 +2732,7 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>10</v>
@@ -2791,7 +2809,7 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>8</v>
@@ -2827,7 +2845,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U30">
         <v>9</v>
@@ -2868,7 +2886,7 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>8</v>
@@ -2945,7 +2963,7 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>10</v>
@@ -2981,7 +2999,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>10</v>
@@ -3022,7 +3040,7 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -3058,7 +3076,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -3099,7 +3117,7 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>8</v>
@@ -3135,7 +3153,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>9</v>
@@ -3176,7 +3194,7 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>10</v>
@@ -3253,7 +3271,7 @@
         <v>4</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I36">
         <v>6</v>
@@ -3289,7 +3307,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U36">
         <v>7</v>
@@ -3330,7 +3348,7 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I37">
         <v>10</v>
@@ -3366,7 +3384,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U37">
         <v>10</v>
@@ -3407,7 +3425,7 @@
         <v>3</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I38">
         <v>5</v>
@@ -3484,7 +3502,7 @@
         <v>10</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I39">
         <v>10</v>
@@ -3561,7 +3579,7 @@
         <v>10</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I40">
         <v>9</v>
@@ -3597,7 +3615,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U40">
         <v>10</v>
@@ -3638,7 +3656,7 @@
         <v>9</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I41">
         <v>6</v>
@@ -3674,7 +3692,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U41">
         <v>6</v>
@@ -3715,7 +3733,7 @@
         <v>10</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I42">
         <v>10</v>
@@ -3792,7 +3810,7 @@
         <v>9</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I43">
         <v>8</v>
@@ -3828,7 +3846,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U43">
         <v>8</v>
@@ -3869,7 +3887,7 @@
         <v>8</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I44">
         <v>6</v>
@@ -3905,7 +3923,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
         <v>8</v>
@@ -3946,7 +3964,7 @@
         <v>9</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I45">
         <v>8</v>
@@ -3982,7 +4000,7 @@
         <v>-1</v>
       </c>
       <c r="T45">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U45">
         <v>9</v>
@@ -4023,7 +4041,7 @@
         <v>10</v>
       </c>
       <c r="H46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I46">
         <v>10</v>
@@ -4210,7 +4228,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -4269,7 +4287,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -4328,7 +4346,7 @@
         <v>96.7</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I6">
         <v>100</v>
@@ -4387,7 +4405,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I7">
         <v>86.7</v>
@@ -4446,7 +4464,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -4505,7 +4523,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -4564,7 +4582,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -4623,7 +4641,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -4682,7 +4700,7 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -4741,7 +4759,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -4800,7 +4818,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -4859,7 +4877,7 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I15">
         <v>93.3</v>
@@ -4918,7 +4936,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -4977,7 +4995,7 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>100</v>
@@ -5036,7 +5054,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -5095,7 +5113,7 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -5154,7 +5172,7 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -5213,7 +5231,7 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I21">
         <v>100</v>
@@ -5272,7 +5290,7 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22">
         <v>100</v>
@@ -5331,7 +5349,7 @@
         <v>93.3</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I23">
         <v>100</v>
@@ -5390,7 +5408,7 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24">
         <v>100</v>
@@ -5449,7 +5467,7 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>100</v>
@@ -5508,7 +5526,7 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26">
         <v>100</v>
@@ -5567,7 +5585,7 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>100</v>
@@ -5626,7 +5644,7 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I28">
         <v>93.3</v>
@@ -5685,7 +5703,7 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>100</v>
@@ -5744,7 +5762,7 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I30">
         <v>86.7</v>
@@ -5803,7 +5821,7 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I31">
         <v>100</v>
@@ -5862,7 +5880,7 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32">
         <v>100</v>
@@ -5921,7 +5939,7 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33">
         <v>100</v>
@@ -5980,7 +5998,7 @@
         <v>100</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I34">
         <v>100</v>
@@ -6039,7 +6057,7 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I35">
         <v>100</v>
@@ -6098,7 +6116,7 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I36">
         <v>100</v>
@@ -6157,7 +6175,7 @@
         <v>100</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I37">
         <v>100</v>
@@ -6216,7 +6234,7 @@
         <v>83.3</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I38">
         <v>86.7</v>
@@ -6275,7 +6293,7 @@
         <v>100</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I39">
         <v>100</v>
@@ -6334,7 +6352,7 @@
         <v>100</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I40">
         <v>100</v>
@@ -6393,7 +6411,7 @@
         <v>100</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I41">
         <v>100</v>
@@ -6452,7 +6470,7 @@
         <v>100</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I42">
         <v>100</v>
@@ -6511,7 +6529,7 @@
         <v>100</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I43">
         <v>100</v>
@@ -6570,7 +6588,7 @@
         <v>100</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I44">
         <v>100</v>
@@ -6629,7 +6647,7 @@
         <v>100</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I45">
         <v>100</v>
@@ -6688,7 +6706,7 @@
         <v>100</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I46">
         <v>100</v>
@@ -6787,19 +6805,19 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>86</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>14</v>
+        <v>18.6</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7009,7 +7027,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7047,10 +7065,10 @@
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -7070,10 +7088,10 @@
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -7093,10 +7111,10 @@
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -7110,22 +7128,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920114</v>
+        <v>22330051920107</v>
       </c>
       <c r="B5" t="s">
         <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7133,24 +7151,70 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920121</v>
+        <v>22330051920114</v>
       </c>
       <c r="B6" t="s">
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920122</v>
+      </c>
+      <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920121</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" t="s">
         <v>87</v>
       </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="D8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
         <v>69</v>
       </c>
-      <c r="G6">
+      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ALCM - Estadisticos 20222.xlsx
+++ b/grupos/2ALCM - Estadisticos 20222.xlsx
@@ -4210,7 +4210,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -4234,34 +4234,34 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>105</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K4">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>116.7</v>
+        <v>98.5</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4269,7 +4269,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -4287,40 +4287,40 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="I5">
         <v>100</v>
       </c>
       <c r="J5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>100</v>
       </c>
       <c r="L5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -4328,7 +4328,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -4346,13 +4346,13 @@
         <v>96.7</v>
       </c>
       <c r="H6">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="I6">
         <v>100</v>
       </c>
       <c r="J6">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -4361,25 +4361,25 @@
         <v>100</v>
       </c>
       <c r="M6">
-        <v>120</v>
+        <v>98.5</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4387,7 +4387,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="C7">
         <v>80</v>
@@ -4405,40 +4405,40 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>50</v>
+        <v>56.8</v>
       </c>
       <c r="I7">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="J7">
-        <v>95</v>
+        <v>52.4</v>
       </c>
       <c r="K7">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L7">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="M7">
-        <v>111.7</v>
+        <v>96.2</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>56.8</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>52.4</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4446,7 +4446,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -4464,40 +4464,40 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I8">
         <v>100</v>
       </c>
       <c r="J8">
-        <v>110</v>
+        <v>95.2</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L8">
         <v>95</v>
       </c>
       <c r="M8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4505,7 +4505,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -4523,40 +4523,40 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="I9">
         <v>100</v>
       </c>
       <c r="J9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4564,7 +4564,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -4582,13 +4582,13 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="I10">
         <v>100</v>
       </c>
       <c r="J10">
-        <v>110</v>
+        <v>95.2</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -4597,25 +4597,25 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>116.7</v>
+        <v>98.5</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4623,7 +4623,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4641,40 +4641,40 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="I11">
         <v>100</v>
       </c>
       <c r="J11">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K11">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4682,7 +4682,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -4706,7 +4706,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -4715,25 +4715,25 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4741,7 +4741,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -4765,7 +4765,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -4774,25 +4774,25 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4800,7 +4800,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -4818,13 +4818,13 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="I14">
         <v>100</v>
       </c>
       <c r="J14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -4833,25 +4833,25 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4859,7 +4859,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -4877,13 +4877,13 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>95</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I15">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="J15">
-        <v>105</v>
+        <v>90.5</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -4892,25 +4892,25 @@
         <v>100</v>
       </c>
       <c r="M15">
-        <v>116.7</v>
+        <v>98.5</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4918,7 +4918,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -4936,40 +4936,40 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I16">
         <v>100</v>
       </c>
       <c r="J16">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M16">
-        <v>116.7</v>
+        <v>98.5</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4977,7 +4977,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -5001,7 +5001,7 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -5010,25 +5010,25 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -5036,7 +5036,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -5054,40 +5054,40 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I18">
         <v>100</v>
       </c>
       <c r="J18">
-        <v>105</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K18">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -5095,7 +5095,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -5113,40 +5113,40 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="I19">
         <v>100</v>
       </c>
       <c r="J19">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -5154,7 +5154,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -5172,40 +5172,40 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I20">
         <v>100</v>
       </c>
       <c r="J20">
-        <v>105</v>
+        <v>90.5</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M20">
-        <v>115</v>
+        <v>97.7</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -5213,7 +5213,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -5231,13 +5231,13 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="I21">
         <v>100</v>
       </c>
       <c r="J21">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -5246,25 +5246,25 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -5272,7 +5272,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -5296,7 +5296,7 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -5305,25 +5305,25 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -5331,7 +5331,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>85</v>
+        <v>70.8</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -5349,40 +5349,40 @@
         <v>93.3</v>
       </c>
       <c r="H23">
-        <v>60</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I23">
         <v>100</v>
       </c>
       <c r="J23">
-        <v>85</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K23">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="L23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M23">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="N23">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="O23">
+        <v>100</v>
+      </c>
+      <c r="P23">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="Q23">
+        <v>84</v>
+      </c>
+      <c r="R23">
         <v>95</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
       <c r="S23">
-        <v>0</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5390,7 +5390,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -5408,13 +5408,13 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I24">
         <v>100</v>
       </c>
       <c r="J24">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -5423,25 +5423,25 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5449,7 +5449,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -5473,7 +5473,7 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -5482,25 +5482,25 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5508,7 +5508,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -5526,40 +5526,40 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I26">
         <v>100</v>
       </c>
       <c r="J26">
-        <v>105</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5567,7 +5567,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -5591,7 +5591,7 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -5600,25 +5600,25 @@
         <v>100</v>
       </c>
       <c r="M27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5626,7 +5626,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -5644,40 +5644,40 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>80</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I28">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="J28">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="K28">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="L28">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="M28">
-        <v>113.3</v>
+        <v>97</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5685,7 +5685,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -5709,7 +5709,7 @@
         <v>100</v>
       </c>
       <c r="J29">
-        <v>105</v>
+        <v>95.2</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -5718,25 +5718,25 @@
         <v>100</v>
       </c>
       <c r="M29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5744,7 +5744,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -5762,40 +5762,40 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="I30">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="J30">
-        <v>105</v>
+        <v>95.2</v>
       </c>
       <c r="K30">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L30">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M30">
-        <v>113.3</v>
+        <v>97</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5803,7 +5803,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -5821,40 +5821,40 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="I31">
         <v>100</v>
       </c>
       <c r="J31">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K31">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L31">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M31">
-        <v>101.7</v>
+        <v>91.7</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5862,7 +5862,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -5886,7 +5886,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -5895,25 +5895,25 @@
         <v>100</v>
       </c>
       <c r="M32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5921,7 +5921,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -5945,7 +5945,7 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -5954,25 +5954,25 @@
         <v>100</v>
       </c>
       <c r="M33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5980,7 +5980,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -5998,13 +5998,13 @@
         <v>100</v>
       </c>
       <c r="H34">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="I34">
         <v>100</v>
       </c>
       <c r="J34">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -6013,25 +6013,25 @@
         <v>100</v>
       </c>
       <c r="M34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -6039,7 +6039,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -6063,7 +6063,7 @@
         <v>100</v>
       </c>
       <c r="J35">
-        <v>105</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K35">
         <v>100</v>
@@ -6072,25 +6072,25 @@
         <v>100</v>
       </c>
       <c r="M35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -6098,7 +6098,7 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -6116,13 +6116,13 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>95</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I36">
         <v>100</v>
       </c>
       <c r="J36">
-        <v>95</v>
+        <v>83.3</v>
       </c>
       <c r="K36">
         <v>100</v>
@@ -6131,25 +6131,25 @@
         <v>100</v>
       </c>
       <c r="M36">
-        <v>116.7</v>
+        <v>98.5</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -6157,7 +6157,7 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -6181,7 +6181,7 @@
         <v>100</v>
       </c>
       <c r="J37">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K37">
         <v>100</v>
@@ -6190,25 +6190,25 @@
         <v>100</v>
       </c>
       <c r="M37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -6216,7 +6216,7 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="C38">
         <v>80</v>
@@ -6234,40 +6234,40 @@
         <v>83.3</v>
       </c>
       <c r="H38">
-        <v>60</v>
+        <v>72.7</v>
       </c>
       <c r="I38">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="J38">
-        <v>85</v>
+        <v>52.4</v>
       </c>
       <c r="K38">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L38">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="M38">
-        <v>111.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>52.4</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -6275,7 +6275,7 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -6299,7 +6299,7 @@
         <v>100</v>
       </c>
       <c r="J39">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K39">
         <v>100</v>
@@ -6308,25 +6308,25 @@
         <v>100</v>
       </c>
       <c r="M39">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -6334,7 +6334,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -6352,40 +6352,40 @@
         <v>100</v>
       </c>
       <c r="H40">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="I40">
         <v>100</v>
       </c>
       <c r="J40">
-        <v>105</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K40">
         <v>100</v>
       </c>
       <c r="L40">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M40">
-        <v>113.3</v>
+        <v>97</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -6393,7 +6393,7 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -6411,40 +6411,40 @@
         <v>100</v>
       </c>
       <c r="H41">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="I41">
         <v>100</v>
       </c>
       <c r="J41">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K41">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L41">
         <v>100</v>
       </c>
       <c r="M41">
-        <v>116.7</v>
+        <v>98.5</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -6452,7 +6452,7 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C42">
         <v>100</v>
@@ -6476,7 +6476,7 @@
         <v>100</v>
       </c>
       <c r="J42">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K42">
         <v>100</v>
@@ -6485,25 +6485,25 @@
         <v>100</v>
       </c>
       <c r="M42">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -6511,7 +6511,7 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -6529,40 +6529,40 @@
         <v>100</v>
       </c>
       <c r="H43">
+        <v>93.2</v>
+      </c>
+      <c r="I43">
+        <v>100</v>
+      </c>
+      <c r="J43">
+        <v>85.7</v>
+      </c>
+      <c r="K43">
+        <v>96</v>
+      </c>
+      <c r="L43">
         <v>90</v>
       </c>
-      <c r="I43">
-        <v>100</v>
-      </c>
-      <c r="J43">
+      <c r="M43">
+        <v>94.7</v>
+      </c>
+      <c r="N43">
+        <v>93.2</v>
+      </c>
+      <c r="O43">
+        <v>100</v>
+      </c>
+      <c r="P43">
+        <v>85.7</v>
+      </c>
+      <c r="Q43">
+        <v>96</v>
+      </c>
+      <c r="R43">
         <v>90</v>
       </c>
-      <c r="K43">
-        <v>92</v>
-      </c>
-      <c r="L43">
-        <v>80</v>
-      </c>
-      <c r="M43">
-        <v>108.3</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
-        <v>0</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
       <c r="S43">
-        <v>0</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -6570,7 +6570,7 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -6594,7 +6594,7 @@
         <v>100</v>
       </c>
       <c r="J44">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K44">
         <v>100</v>
@@ -6603,25 +6603,25 @@
         <v>100</v>
       </c>
       <c r="M44">
-        <v>116.7</v>
+        <v>98.5</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -6629,7 +6629,7 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C45">
         <v>100</v>
@@ -6647,13 +6647,13 @@
         <v>100</v>
       </c>
       <c r="H45">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="I45">
         <v>100</v>
       </c>
       <c r="J45">
-        <v>105</v>
+        <v>95.2</v>
       </c>
       <c r="K45">
         <v>100</v>
@@ -6662,25 +6662,25 @@
         <v>100</v>
       </c>
       <c r="M45">
-        <v>116.7</v>
+        <v>98.5</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="46" spans="1:19">
@@ -6688,7 +6688,7 @@
         <v>54</v>
       </c>
       <c r="B46">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -6712,7 +6712,7 @@
         <v>100</v>
       </c>
       <c r="J46">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="K46">
         <v>100</v>
@@ -6721,25 +6721,25 @@
         <v>100</v>
       </c>
       <c r="M46">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ALCM - Estadisticos 20222.xlsx
+++ b/grupos/2ALCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="93">
   <si>
     <t>Materia</t>
   </si>
@@ -224,15 +224,15 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
@@ -248,52 +248,49 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>JALAPA</t>
+  </si>
+  <si>
     <t>LARRACILLA</t>
   </si>
   <si>
-    <t>JALAPA</t>
-  </si>
-  <si>
     <t>OLMOS</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>TEPOLE</t>
   </si>
   <si>
     <t>TELE</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
     <t>GIL</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
     <t>MONSERRAT</t>
   </si>
   <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
     <t>AHILY</t>
-  </si>
-  <si>
-    <t>ILEANA</t>
   </si>
   <si>
     <t>JESUS</t>
@@ -828,7 +825,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -840,7 +837,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -905,7 +902,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -917,7 +914,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>7</v>
@@ -982,7 +979,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -994,13 +991,13 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>7</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1012,7 +1009,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1059,7 +1056,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1071,7 +1068,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -1136,7 +1133,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1148,13 +1145,13 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>7</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1166,7 +1163,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1213,7 +1210,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1225,7 +1222,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>7</v>
@@ -1290,7 +1287,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1302,7 +1299,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1367,7 +1364,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1379,7 +1376,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -1397,7 +1394,7 @@
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1444,7 +1441,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1456,13 +1453,13 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>8</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1521,7 +1518,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1533,13 +1530,13 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>7</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1598,7 +1595,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1610,7 +1607,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -1675,7 +1672,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1687,13 +1684,13 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>6</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>10</v>
@@ -1752,7 +1749,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1764,7 +1761,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>6</v>
@@ -1829,7 +1826,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1841,13 +1838,13 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>8</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -1906,7 +1903,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -1918,13 +1915,13 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>6</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -1983,7 +1980,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -1995,7 +1992,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>6</v>
@@ -2060,7 +2057,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2072,7 +2069,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -2090,7 +2087,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2137,7 +2134,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2149,7 +2146,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>5</v>
@@ -2167,7 +2164,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2214,7 +2211,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2226,13 +2223,13 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>7</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2291,7 +2288,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2303,7 +2300,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>5</v>
@@ -2368,7 +2365,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2380,7 +2377,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2445,7 +2442,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2457,7 +2454,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2522,7 +2519,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2534,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2552,7 +2549,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2599,7 +2596,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2611,7 +2608,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2676,7 +2673,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2688,7 +2685,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>5</v>
@@ -2706,7 +2703,7 @@
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2753,7 +2750,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -2765,13 +2762,13 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>8</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>10</v>
@@ -2830,7 +2827,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -2842,13 +2839,13 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>5</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -2907,7 +2904,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -2919,7 +2916,7 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>6</v>
@@ -2984,7 +2981,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -2996,13 +2993,13 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>7</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3061,7 +3058,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3073,13 +3070,13 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>7</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -3138,7 +3135,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3150,7 +3147,7 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>6</v>
@@ -3215,7 +3212,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3227,13 +3224,13 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>7</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -3245,7 +3242,7 @@
         <v>7</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3292,7 +3289,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3304,7 +3301,7 @@
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
         <v>7</v>
@@ -3322,7 +3319,7 @@
         <v>7</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3369,7 +3366,7 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3381,13 +3378,13 @@
         <v>-1</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>7</v>
       </c>
       <c r="U37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>10</v>
@@ -3446,7 +3443,7 @@
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3458,7 +3455,7 @@
         <v>-1</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
         <v>5</v>
@@ -3476,7 +3473,7 @@
         <v>6</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3523,7 +3520,7 @@
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -3535,7 +3532,7 @@
         <v>-1</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>10</v>
@@ -3600,7 +3597,7 @@
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -3612,7 +3609,7 @@
         <v>-1</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
         <v>7</v>
@@ -3677,7 +3674,7 @@
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -3689,7 +3686,7 @@
         <v>-1</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T41">
         <v>7</v>
@@ -3754,7 +3751,7 @@
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -3766,7 +3763,7 @@
         <v>-1</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T42">
         <v>9</v>
@@ -3831,7 +3828,7 @@
         <v>-1</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P43">
         <v>-1</v>
@@ -3843,13 +3840,13 @@
         <v>-1</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T43">
         <v>6</v>
       </c>
       <c r="U43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V43">
         <v>8</v>
@@ -3861,7 +3858,7 @@
         <v>5</v>
       </c>
       <c r="Y43">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3908,7 +3905,7 @@
         <v>-1</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P44">
         <v>-1</v>
@@ -3920,13 +3917,13 @@
         <v>-1</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T44">
         <v>5</v>
       </c>
       <c r="U44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V44">
         <v>9</v>
@@ -3938,7 +3935,7 @@
         <v>7</v>
       </c>
       <c r="Y44">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -3985,7 +3982,7 @@
         <v>-1</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P45">
         <v>-1</v>
@@ -3997,7 +3994,7 @@
         <v>-1</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T45">
         <v>7</v>
@@ -4062,7 +4059,7 @@
         <v>-1</v>
       </c>
       <c r="O46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P46">
         <v>-1</v>
@@ -4074,7 +4071,7 @@
         <v>-1</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T46">
         <v>9</v>
@@ -4261,7 +4258,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4379,7 +4376,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4426,7 +4423,7 @@
         <v>56.8</v>
       </c>
       <c r="O7">
-        <v>83.3</v>
+        <v>60.4</v>
       </c>
       <c r="P7">
         <v>52.4</v>
@@ -4438,7 +4435,7 @@
         <v>75</v>
       </c>
       <c r="S7">
-        <v>96.2</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4615,7 +4612,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4898,7 +4895,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="O15">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P15">
         <v>90.5</v>
@@ -4910,7 +4907,7 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4969,7 +4966,7 @@
         <v>97.5</v>
       </c>
       <c r="S16">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -5205,7 +5202,7 @@
         <v>95</v>
       </c>
       <c r="S20">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -5370,7 +5367,7 @@
         <v>65.90000000000001</v>
       </c>
       <c r="O23">
-        <v>100</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="P23">
         <v>78.59999999999999</v>
@@ -5382,7 +5379,7 @@
         <v>95</v>
       </c>
       <c r="S23">
-        <v>85.59999999999999</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5665,7 +5662,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="O28">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P28">
         <v>90.5</v>
@@ -5677,7 +5674,7 @@
         <v>87.5</v>
       </c>
       <c r="S28">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5783,7 +5780,7 @@
         <v>93.2</v>
       </c>
       <c r="O30">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="P30">
         <v>95.2</v>
@@ -5795,7 +5792,7 @@
         <v>97.5</v>
       </c>
       <c r="S30">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5854,7 +5851,7 @@
         <v>97.5</v>
       </c>
       <c r="S31">
-        <v>91.7</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -6149,7 +6146,7 @@
         <v>100</v>
       </c>
       <c r="S36">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -6255,7 +6252,7 @@
         <v>72.7</v>
       </c>
       <c r="O38">
-        <v>83.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="P38">
         <v>52.4</v>
@@ -6267,7 +6264,7 @@
         <v>92.5</v>
       </c>
       <c r="S38">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -6385,7 +6382,7 @@
         <v>97.5</v>
       </c>
       <c r="S40">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -6444,7 +6441,7 @@
         <v>100</v>
       </c>
       <c r="S41">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -6562,7 +6559,7 @@
         <v>90</v>
       </c>
       <c r="S43">
-        <v>94.7</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -6621,7 +6618,7 @@
         <v>100</v>
       </c>
       <c r="S44">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -6680,7 +6677,7 @@
         <v>100</v>
       </c>
       <c r="S45">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:19">
@@ -6828,7 +6825,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
@@ -6837,19 +6834,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G3" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6860,10 +6857,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4">
         <v>43</v>
@@ -6881,7 +6878,7 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6892,7 +6889,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
@@ -6901,19 +6898,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>93</v>
+        <v>95.3</v>
       </c>
       <c r="G5" s="2">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6924,7 +6921,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
@@ -6945,7 +6942,7 @@
         <v>4.7</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7059,7 +7056,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920340</v>
+        <v>22330051920105</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
@@ -7068,7 +7065,7 @@
         <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -7082,7 +7079,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920340</v>
+        <v>22330051920105</v>
       </c>
       <c r="B3" t="s">
         <v>76</v>
@@ -7091,10 +7088,10 @@
         <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>68</v>
@@ -7114,7 +7111,7 @@
         <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -7128,7 +7125,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920107</v>
+        <v>22330051920340</v>
       </c>
       <c r="B5" t="s">
         <v>78</v>
@@ -7137,7 +7134,7 @@
         <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -7151,22 +7148,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920114</v>
+        <v>22330051920107</v>
       </c>
       <c r="B6" t="s">
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7180,10 +7177,10 @@
         <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -7203,16 +7200,16 @@
         <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8">
         <v>5</v>

--- a/grupos/2ALCM - Estadisticos 20222.xlsx
+++ b/grupos/2ALCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="96">
   <si>
     <t>Materia</t>
   </si>
@@ -224,6 +224,9 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
@@ -233,9 +236,6 @@
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -260,6 +260,9 @@
     <t>OLMOS</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>TEPOLE</t>
   </si>
   <si>
@@ -275,6 +278,9 @@
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
     <t>GIL</t>
   </si>
   <si>
@@ -291,6 +297,9 @@
   </si>
   <si>
     <t>AHILY</t>
+  </si>
+  <si>
+    <t>ILEANA</t>
   </si>
   <si>
     <t>JESUS</t>
@@ -828,7 +837,7 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -905,7 +914,7 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -982,7 +991,7 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1000,7 +1009,7 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1059,7 +1068,7 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1136,7 +1145,7 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1213,7 +1222,7 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1231,7 +1240,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1290,7 +1299,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1367,7 +1376,7 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1444,7 +1453,7 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1462,7 +1471,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1521,7 +1530,7 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1539,7 +1548,7 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1598,7 +1607,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1675,7 +1684,7 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1693,7 +1702,7 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1752,7 +1761,7 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -1829,7 +1838,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -1847,7 +1856,7 @@
         <v>9</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -1906,7 +1915,7 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -1983,7 +1992,7 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2001,7 +2010,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2060,7 +2069,7 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2078,7 +2087,7 @@
         <v>6</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2137,7 +2146,7 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2155,7 +2164,7 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2214,7 +2223,7 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2232,7 +2241,7 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2291,7 +2300,7 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2309,7 +2318,7 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2368,7 +2377,7 @@
         <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2386,7 +2395,7 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2445,7 +2454,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2522,7 +2531,7 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2540,7 +2549,7 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2599,7 +2608,7 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2676,7 +2685,7 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2694,7 +2703,7 @@
         <v>6</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2753,7 +2762,7 @@
         <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -2830,7 +2839,7 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -2848,7 +2857,7 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -2907,7 +2916,7 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -2925,7 +2934,7 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -2984,7 +2993,7 @@
         <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3061,7 +3070,7 @@
         <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3138,7 +3147,7 @@
         <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3156,7 +3165,7 @@
         <v>9</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>8</v>
@@ -3215,7 +3224,7 @@
         <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3292,7 +3301,7 @@
         <v>7</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -3310,7 +3319,7 @@
         <v>7</v>
       </c>
       <c r="V36">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>8</v>
@@ -3369,7 +3378,7 @@
         <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -3446,7 +3455,7 @@
         <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -3464,7 +3473,7 @@
         <v>5</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W38">
         <v>5</v>
@@ -3523,7 +3532,7 @@
         <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -3600,7 +3609,7 @@
         <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -3677,7 +3686,7 @@
         <v>6</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -3695,7 +3704,7 @@
         <v>6</v>
       </c>
       <c r="V41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W41">
         <v>8</v>
@@ -3754,7 +3763,7 @@
         <v>10</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q42">
         <v>-1</v>
@@ -3831,7 +3840,7 @@
         <v>6</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q43">
         <v>-1</v>
@@ -3849,7 +3858,7 @@
         <v>7</v>
       </c>
       <c r="V43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W43">
         <v>7</v>
@@ -3908,7 +3917,7 @@
         <v>7</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q44">
         <v>-1</v>
@@ -3926,7 +3935,7 @@
         <v>7</v>
       </c>
       <c r="V44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W44">
         <v>9</v>
@@ -3985,7 +3994,7 @@
         <v>9</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q45">
         <v>-1</v>
@@ -4062,7 +4071,7 @@
         <v>10</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q46">
         <v>-1</v>
@@ -4249,7 +4258,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>97.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="Q4">
         <v>96</v>
@@ -4367,7 +4376,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4426,7 +4435,7 @@
         <v>60.4</v>
       </c>
       <c r="P7">
-        <v>52.4</v>
+        <v>62.5</v>
       </c>
       <c r="Q7">
         <v>82</v>
@@ -4485,7 +4494,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="Q8">
         <v>98</v>
@@ -4544,7 +4553,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -4603,7 +4612,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>95.2</v>
+        <v>93.8</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4662,7 +4671,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q11">
         <v>98</v>
@@ -4721,7 +4730,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>97.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4780,7 +4789,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>97.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4898,7 +4907,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="P15">
-        <v>90.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -5016,7 +5025,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -5075,7 +5084,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>92.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="Q18">
         <v>98</v>
@@ -5134,7 +5143,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>97.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -5193,7 +5202,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>90.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -5252,7 +5261,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>95.2</v>
+        <v>87.5</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -5311,7 +5320,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -5370,7 +5379,7 @@
         <v>89.59999999999999</v>
       </c>
       <c r="P23">
-        <v>78.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Q23">
         <v>84</v>
@@ -5547,7 +5556,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>97.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="Q26">
         <v>96</v>
@@ -5665,7 +5674,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="P28">
-        <v>90.5</v>
+        <v>81.3</v>
       </c>
       <c r="Q28">
         <v>86</v>
@@ -5724,7 +5733,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>95.2</v>
+        <v>93.8</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5783,7 +5792,7 @@
         <v>95.8</v>
       </c>
       <c r="P30">
-        <v>95.2</v>
+        <v>93.8</v>
       </c>
       <c r="Q30">
         <v>94</v>
@@ -6019,7 +6028,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -6078,7 +6087,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -6137,7 +6146,7 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>83.3</v>
+        <v>79.7</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -6196,7 +6205,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -6255,7 +6264,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="P38">
-        <v>52.4</v>
+        <v>60.9</v>
       </c>
       <c r="Q38">
         <v>94</v>
@@ -6373,7 +6382,7 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -6432,7 +6441,7 @@
         <v>100</v>
       </c>
       <c r="P41">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q41">
         <v>98</v>
@@ -6550,7 +6559,7 @@
         <v>100</v>
       </c>
       <c r="P43">
-        <v>85.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q43">
         <v>96</v>
@@ -6668,7 +6677,7 @@
         <v>100</v>
       </c>
       <c r="P45">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="Q45">
         <v>100</v>
@@ -6825,7 +6834,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
@@ -6834,19 +6843,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>93</v>
+        <v>90.7</v>
       </c>
       <c r="G3" s="2">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6857,10 +6866,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>43</v>
@@ -6878,7 +6887,7 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6889,7 +6898,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
@@ -6898,19 +6907,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>95.3</v>
+        <v>93</v>
       </c>
       <c r="G5" s="2">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6921,7 +6930,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
@@ -6942,7 +6951,7 @@
         <v>4.7</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6953,7 +6962,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -6962,19 +6971,19 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="G7" s="2">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7024,7 +7033,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7062,10 +7071,10 @@
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -7085,16 +7094,16 @@
         <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7108,10 +7117,10 @@
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -7131,10 +7140,10 @@
         <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -7154,10 +7163,10 @@
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -7171,22 +7180,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920122</v>
+        <v>22330051920114</v>
       </c>
       <c r="B7" t="s">
         <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7194,24 +7203,47 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920121</v>
+        <v>22330051920122</v>
       </c>
       <c r="B8" t="s">
         <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920121</v>
+      </c>
+      <c r="B9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ALCM - Estadisticos 20222.xlsx
+++ b/grupos/2ALCM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="93">
   <si>
     <t>Materia</t>
   </si>
@@ -227,15 +227,15 @@
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -248,64 +248,55 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JALAPA</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>JALAPA</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
     <t>OLMOS</t>
   </si>
   <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>TELE</t>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
+    <t>ANETTE</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
   </si>
   <si>
     <t>VALERIA</t>
   </si>
   <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
     <t>AHILY</t>
   </si>
   <si>
     <t>ILEANA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>BETSABETH</t>
   </si>
 </sst>
 </file>
@@ -831,7 +822,7 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>9</v>
@@ -840,16 +831,16 @@
         <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>10</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -861,7 +852,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -908,7 +899,7 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>9</v>
@@ -917,16 +908,16 @@
         <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>10</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -938,7 +929,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>9</v>
@@ -985,7 +976,7 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>8</v>
@@ -994,10 +985,10 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -1015,7 +1006,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1062,7 +1053,7 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -1071,10 +1062,10 @@
         <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>5</v>
@@ -1139,7 +1130,7 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1148,16 +1139,16 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>9</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U8">
         <v>6</v>
@@ -1166,10 +1157,10 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1216,7 +1207,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
         <v>10</v>
@@ -1225,16 +1216,16 @@
         <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>9</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1293,7 +1284,7 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -1302,10 +1293,10 @@
         <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>10</v>
@@ -1370,7 +1361,7 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1379,16 +1370,16 @@
         <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>8</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1400,7 +1391,7 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1447,7 +1438,7 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>8</v>
@@ -1456,10 +1447,10 @@
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>10</v>
@@ -1524,7 +1515,7 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>7</v>
@@ -1533,16 +1524,16 @@
         <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>9</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>9</v>
@@ -1551,10 +1542,10 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1601,7 +1592,7 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
         <v>10</v>
@@ -1610,10 +1601,10 @@
         <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>8</v>
@@ -1678,7 +1669,7 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>7</v>
@@ -1687,10 +1678,10 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>9</v>
@@ -1755,7 +1746,7 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>8</v>
@@ -1764,10 +1755,10 @@
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>8</v>
@@ -1782,10 +1773,10 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1832,7 +1823,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>8</v>
@@ -1841,16 +1832,16 @@
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>10</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>9</v>
@@ -1862,7 +1853,7 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -1909,7 +1900,7 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>10</v>
@@ -1918,10 +1909,10 @@
         <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>9</v>
@@ -1936,10 +1927,10 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -1986,7 +1977,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>7</v>
@@ -1995,16 +1986,16 @@
         <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>9</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>8</v>
@@ -2063,7 +2054,7 @@
         <v>4</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -2072,10 +2063,10 @@
         <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>8</v>
@@ -2093,7 +2084,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2140,7 +2131,7 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2149,10 +2140,10 @@
         <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>8</v>
@@ -2167,7 +2158,7 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2217,7 +2208,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>8</v>
@@ -2226,10 +2217,10 @@
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>9</v>
@@ -2294,7 +2285,7 @@
         <v>3</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
         <v>6</v>
@@ -2303,10 +2294,10 @@
         <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>5</v>
@@ -2371,7 +2362,7 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
         <v>9</v>
@@ -2380,16 +2371,16 @@
         <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>9</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2401,7 +2392,7 @@
         <v>10</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2448,7 +2439,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
         <v>10</v>
@@ -2457,10 +2448,10 @@
         <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>10</v>
@@ -2525,7 +2516,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>9</v>
@@ -2534,10 +2525,10 @@
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>10</v>
@@ -2602,7 +2593,7 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>10</v>
@@ -2611,10 +2602,10 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>10</v>
@@ -2679,7 +2670,7 @@
         <v>4</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -2688,10 +2679,10 @@
         <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>8</v>
@@ -2709,7 +2700,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -2756,7 +2747,7 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>9</v>
@@ -2765,10 +2756,10 @@
         <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>10</v>
@@ -2833,7 +2824,7 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>7</v>
@@ -2842,10 +2833,10 @@
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
         <v>8</v>
@@ -2860,7 +2851,7 @@
         <v>7</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -2910,7 +2901,7 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
         <v>8</v>
@@ -2919,10 +2910,10 @@
         <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>8</v>
@@ -2937,10 +2928,10 @@
         <v>7</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -2987,7 +2978,7 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>9</v>
@@ -2996,10 +2987,10 @@
         <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>10</v>
@@ -3017,7 +3008,7 @@
         <v>9</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3064,7 +3055,7 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>7</v>
@@ -3073,10 +3064,10 @@
         <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
         <v>10</v>
@@ -3141,7 +3132,7 @@
         <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
         <v>9</v>
@@ -3150,10 +3141,10 @@
         <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
         <v>10</v>
@@ -3218,7 +3209,7 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <v>9</v>
@@ -3227,16 +3218,16 @@
         <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>9</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>9</v>
@@ -3245,10 +3236,10 @@
         <v>10</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>8</v>
@@ -3295,7 +3286,7 @@
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
         <v>7</v>
@@ -3304,16 +3295,16 @@
         <v>9</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
         <v>9</v>
       </c>
       <c r="T36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>7</v>
@@ -3372,7 +3363,7 @@
         <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
         <v>9</v>
@@ -3381,10 +3372,10 @@
         <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
         <v>10</v>
@@ -3449,7 +3440,7 @@
         <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O38">
         <v>6</v>
@@ -3458,10 +3449,10 @@
         <v>5</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
         <v>9</v>
@@ -3476,7 +3467,7 @@
         <v>5</v>
       </c>
       <c r="W38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X38">
         <v>6</v>
@@ -3526,7 +3517,7 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O39">
         <v>10</v>
@@ -3535,16 +3526,16 @@
         <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
         <v>10</v>
       </c>
       <c r="T39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U39">
         <v>10</v>
@@ -3603,7 +3594,7 @@
         <v>8</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O40">
         <v>10</v>
@@ -3612,10 +3603,10 @@
         <v>10</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
         <v>10</v>
@@ -3630,10 +3621,10 @@
         <v>10</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y40">
         <v>9</v>
@@ -3680,7 +3671,7 @@
         <v>9</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O41">
         <v>6</v>
@@ -3689,10 +3680,10 @@
         <v>9</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S41">
         <v>9</v>
@@ -3710,7 +3701,7 @@
         <v>8</v>
       </c>
       <c r="X41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y41">
         <v>9</v>
@@ -3757,7 +3748,7 @@
         <v>10</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>10</v>
@@ -3766,16 +3757,16 @@
         <v>10</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
         <v>10</v>
       </c>
       <c r="T42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U42">
         <v>10</v>
@@ -3834,7 +3825,7 @@
         <v>6</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>6</v>
@@ -3843,10 +3834,10 @@
         <v>6</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S43">
         <v>5</v>
@@ -3861,10 +3852,10 @@
         <v>7</v>
       </c>
       <c r="W43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y43">
         <v>7</v>
@@ -3911,7 +3902,7 @@
         <v>6</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O44">
         <v>7</v>
@@ -3920,16 +3911,16 @@
         <v>8</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S44">
         <v>10</v>
       </c>
       <c r="T44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U44">
         <v>7</v>
@@ -3988,7 +3979,7 @@
         <v>9</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O45">
         <v>9</v>
@@ -3997,10 +3988,10 @@
         <v>10</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S45">
         <v>10</v>
@@ -4065,7 +4056,7 @@
         <v>10</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O46">
         <v>10</v>
@@ -4074,10 +4065,10 @@
         <v>10</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S46">
         <v>10</v>
@@ -4252,7 +4243,7 @@
         <v>98.5</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -4261,10 +4252,10 @@
         <v>95.3</v>
       </c>
       <c r="Q4">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S4">
         <v>99</v>
@@ -4311,7 +4302,7 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -4323,7 +4314,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4370,7 +4361,7 @@
         <v>98.5</v>
       </c>
       <c r="N6">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -4429,7 +4420,7 @@
         <v>96.2</v>
       </c>
       <c r="N7">
-        <v>56.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="O7">
         <v>60.4</v>
@@ -4438,10 +4429,10 @@
         <v>62.5</v>
       </c>
       <c r="Q7">
-        <v>82</v>
+        <v>76.3</v>
       </c>
       <c r="R7">
-        <v>75</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="S7">
         <v>95.3</v>
@@ -4488,7 +4479,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -4497,10 +4488,10 @@
         <v>95.3</v>
       </c>
       <c r="Q8">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="R8">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -4547,7 +4538,7 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -4559,7 +4550,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4606,7 +4597,7 @@
         <v>98.5</v>
       </c>
       <c r="N10">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -4665,7 +4656,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -4674,7 +4665,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="Q11">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -4783,7 +4774,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -4795,7 +4786,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -4842,7 +4833,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -4901,7 +4892,7 @@
         <v>98.5</v>
       </c>
       <c r="N15">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O15">
         <v>97.90000000000001</v>
@@ -4910,7 +4901,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -4960,7 +4951,7 @@
         <v>98.5</v>
       </c>
       <c r="N16">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -4969,10 +4960,10 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R16">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S16">
         <v>99</v>
@@ -5078,7 +5069,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -5087,10 +5078,10 @@
         <v>92.2</v>
       </c>
       <c r="Q18">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="R18">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -5137,7 +5128,7 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -5149,7 +5140,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -5196,7 +5187,7 @@
         <v>97.7</v>
       </c>
       <c r="N20">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -5205,10 +5196,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R20">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="S20">
         <v>98.40000000000001</v>
@@ -5255,7 +5246,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -5323,7 +5314,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -5373,7 +5364,7 @@
         <v>85.59999999999999</v>
       </c>
       <c r="N23">
-        <v>65.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="O23">
         <v>89.59999999999999</v>
@@ -5382,10 +5373,10 @@
         <v>71.90000000000001</v>
       </c>
       <c r="Q23">
-        <v>84</v>
+        <v>71.3</v>
       </c>
       <c r="R23">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S23">
         <v>87</v>
@@ -5432,7 +5423,7 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -5550,7 +5541,7 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -5559,10 +5550,10 @@
         <v>95.3</v>
       </c>
       <c r="Q26">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R26">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -5668,7 +5659,7 @@
         <v>97</v>
       </c>
       <c r="N28">
-        <v>84.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="O28">
         <v>97.90000000000001</v>
@@ -5677,10 +5668,10 @@
         <v>81.3</v>
       </c>
       <c r="Q28">
-        <v>86</v>
+        <v>86.3</v>
       </c>
       <c r="R28">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S28">
         <v>97.90000000000001</v>
@@ -5786,7 +5777,7 @@
         <v>97</v>
       </c>
       <c r="N30">
-        <v>93.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O30">
         <v>95.8</v>
@@ -5795,10 +5786,10 @@
         <v>93.8</v>
       </c>
       <c r="Q30">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="R30">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S30">
         <v>97.90000000000001</v>
@@ -5845,7 +5836,7 @@
         <v>91.7</v>
       </c>
       <c r="N31">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="O31">
         <v>100</v>
@@ -5854,10 +5845,10 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="R31">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S31">
         <v>94.3</v>
@@ -5904,7 +5895,7 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O32">
         <v>100</v>
@@ -6022,7 +6013,7 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -6140,7 +6131,7 @@
         <v>98.5</v>
       </c>
       <c r="N36">
-        <v>88.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O36">
         <v>100</v>
@@ -6149,10 +6140,10 @@
         <v>79.7</v>
       </c>
       <c r="Q36">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R36">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S36">
         <v>99</v>
@@ -6258,7 +6249,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="N38">
-        <v>72.7</v>
+        <v>75</v>
       </c>
       <c r="O38">
         <v>85.40000000000001</v>
@@ -6267,10 +6258,10 @@
         <v>60.9</v>
       </c>
       <c r="Q38">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="R38">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="S38">
         <v>92.2</v>
@@ -6376,7 +6367,7 @@
         <v>97</v>
       </c>
       <c r="N40">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O40">
         <v>100</v>
@@ -6388,7 +6379,7 @@
         <v>100</v>
       </c>
       <c r="R40">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S40">
         <v>97.90000000000001</v>
@@ -6435,7 +6426,7 @@
         <v>98.5</v>
       </c>
       <c r="N41">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O41">
         <v>100</v>
@@ -6444,7 +6435,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="Q41">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="R41">
         <v>100</v>
@@ -6553,7 +6544,7 @@
         <v>94.7</v>
       </c>
       <c r="N43">
-        <v>93.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O43">
         <v>100</v>
@@ -6562,10 +6553,10 @@
         <v>84.40000000000001</v>
       </c>
       <c r="Q43">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R43">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S43">
         <v>96.40000000000001</v>
@@ -6671,7 +6662,7 @@
         <v>98.5</v>
       </c>
       <c r="N45">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O45">
         <v>100</v>
@@ -6823,7 +6814,7 @@
         <v>18.6</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6866,7 +6857,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
@@ -6875,19 +6866,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>93</v>
+        <v>95.3</v>
       </c>
       <c r="G4" s="2">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6898,25 +6889,25 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5">
         <v>43</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>93</v>
+        <v>95.3</v>
       </c>
       <c r="G5" s="2">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="H5">
         <v>8.300000000000001</v>
@@ -6930,10 +6921,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6">
         <v>43</v>
@@ -6962,7 +6953,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -6971,19 +6962,19 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>95.3</v>
+        <v>97.7</v>
       </c>
       <c r="G7" s="2">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7033,7 +7024,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7065,16 +7056,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920105</v>
+        <v>22330051920098</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -7088,22 +7079,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920105</v>
+        <v>22330051920339</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7111,16 +7102,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920339</v>
+        <v>22330051920340</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -7134,16 +7125,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920340</v>
+        <v>22330051920105</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
         <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -7160,13 +7151,13 @@
         <v>22330051920107</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -7183,13 +7174,13 @@
         <v>22330051920114</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
         <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -7198,52 +7189,6 @@
         <v>68</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920122</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920121</v>
-      </c>
-      <c r="B9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>
